--- a/XLS/S3/s3.xlsx
+++ b/XLS/S3/s3.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Mohammed Al-Emara\Documents\GitHub\Statistical-notebook\XLS\S3\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3494A222-0E9B-4FC7-A24D-6CB3378186F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{64A14EF7-B671-4364-8B40-37DB9DDDB7F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" tabRatio="500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="choices" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6660" uniqueCount="2565">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6660" uniqueCount="2566">
   <si>
     <t>list_name</t>
   </si>
@@ -7783,6 +7783,9 @@
   </si>
   <si>
     <t>مقاطعة 9 مجيهيلة الشرقية</t>
+  </si>
+  <si>
+    <t>المناذرة</t>
   </si>
 </sst>
 </file>
@@ -7985,7 +7988,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="66">
+  <cellXfs count="67">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -8161,6 +8164,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="10" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -8556,10 +8562,10 @@
         <v>3</v>
       </c>
       <c r="C12" t="s">
-        <v>14</v>
+        <v>2565</v>
       </c>
       <c r="D12" t="s">
-        <v>14</v>
+        <v>2565</v>
       </c>
     </row>
     <row r="13" spans="1:8" ht="14" x14ac:dyDescent="0.3">
@@ -9369,7 +9375,7 @@
       <c r="A68" t="s">
         <v>80</v>
       </c>
-      <c r="B68" s="47">
+      <c r="B68" s="64">
         <v>1</v>
       </c>
       <c r="C68" s="50" t="s">
@@ -9383,7 +9389,7 @@
       <c r="A69" t="s">
         <v>80</v>
       </c>
-      <c r="B69" s="47">
+      <c r="B69" s="64">
         <v>2</v>
       </c>
       <c r="C69" s="50" t="s">
@@ -9397,7 +9403,7 @@
       <c r="A70" t="s">
         <v>80</v>
       </c>
-      <c r="B70" s="47">
+      <c r="B70" s="64">
         <v>3</v>
       </c>
       <c r="C70" s="50" t="s">
@@ -9411,7 +9417,7 @@
       <c r="A71" t="s">
         <v>80</v>
       </c>
-      <c r="B71" s="47">
+      <c r="B71" s="64">
         <v>4</v>
       </c>
       <c r="C71" s="50" t="s">
@@ -9425,7 +9431,7 @@
       <c r="A72" t="s">
         <v>80</v>
       </c>
-      <c r="B72" s="47">
+      <c r="B72" s="64">
         <v>5</v>
       </c>
       <c r="C72" s="50" t="s">
@@ -35858,8 +35864,8 @@
       </c>
     </row>
     <row r="209" spans="1:18" s="35" customFormat="1" ht="13.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A209" s="64"/>
-      <c r="B209" s="65"/>
+      <c r="A209" s="65"/>
+      <c r="B209" s="66"/>
       <c r="C209" s="37"/>
       <c r="D209" s="37"/>
       <c r="E209" s="37"/>
@@ -36051,7 +36057,7 @@
       <c r="Q220" s="8"/>
       <c r="R220" s="8"/>
     </row>
-    <row r="221" spans="1:18" ht="12.65" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="221" spans="1:18" ht="12.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A221" s="10" t="s">
         <v>322</v>
       </c>
@@ -36063,7 +36069,7 @@
         <v>343</v>
       </c>
     </row>
-    <row r="222" spans="1:18" ht="12.65" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="222" spans="1:18" ht="12.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A222" s="2" t="s">
         <v>252</v>
       </c>
@@ -36076,7 +36082,7 @@
         <v>328</v>
       </c>
     </row>
-    <row r="223" spans="1:18" ht="14" hidden="1" x14ac:dyDescent="0.3">
+    <row r="223" spans="1:18" ht="14" x14ac:dyDescent="0.3">
       <c r="A223" s="2" t="s">
         <v>248</v>
       </c>
@@ -36093,7 +36099,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="224" spans="1:18" ht="14" hidden="1" x14ac:dyDescent="0.3">
+    <row r="224" spans="1:18" ht="14" x14ac:dyDescent="0.3">
       <c r="A224" s="2" t="s">
         <v>248</v>
       </c>
@@ -36111,7 +36117,7 @@
       </c>
       <c r="Q224"/>
     </row>
-    <row r="225" spans="1:18" ht="14" hidden="1" x14ac:dyDescent="0.3">
+    <row r="225" spans="1:18" ht="14" x14ac:dyDescent="0.3">
       <c r="A225" s="2" t="s">
         <v>248</v>
       </c>
@@ -36129,7 +36135,7 @@
       </c>
       <c r="Q225"/>
     </row>
-    <row r="226" spans="1:18" ht="14" hidden="1" x14ac:dyDescent="0.3">
+    <row r="226" spans="1:18" ht="14" x14ac:dyDescent="0.3">
       <c r="A226" s="2" t="s">
         <v>248</v>
       </c>
@@ -36146,17 +36152,17 @@
         <v>259</v>
       </c>
     </row>
-    <row r="227" spans="1:18" ht="12.65" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="227" spans="1:18" ht="12.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A227" s="2" t="s">
         <v>319</v>
       </c>
       <c r="H227" s="12"/>
       <c r="I227" s="12"/>
     </row>
-    <row r="228" spans="1:18" ht="14" hidden="1" x14ac:dyDescent="0.3">
+    <row r="228" spans="1:18" ht="14" x14ac:dyDescent="0.3">
       <c r="H228" s="2"/>
     </row>
-    <row r="229" spans="1:18" ht="12.65" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="229" spans="1:18" ht="12.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A229" s="2" t="s">
         <v>252</v>
       </c>
@@ -36169,7 +36175,7 @@
         <v>328</v>
       </c>
     </row>
-    <row r="230" spans="1:18" ht="14" hidden="1" x14ac:dyDescent="0.3">
+    <row r="230" spans="1:18" ht="14" x14ac:dyDescent="0.3">
       <c r="A230" s="2" t="s">
         <v>248</v>
       </c>
@@ -36187,7 +36193,7 @@
       </c>
       <c r="Q230" s="16"/>
     </row>
-    <row r="231" spans="1:18" ht="14" hidden="1" x14ac:dyDescent="0.3">
+    <row r="231" spans="1:18" ht="14" x14ac:dyDescent="0.3">
       <c r="A231" s="2" t="s">
         <v>275</v>
       </c>
@@ -36211,7 +36217,7 @@
         <v>560</v>
       </c>
     </row>
-    <row r="232" spans="1:18" ht="14" hidden="1" x14ac:dyDescent="0.3">
+    <row r="232" spans="1:18" ht="14" x14ac:dyDescent="0.3">
       <c r="A232" s="2" t="s">
         <v>275</v>
       </c>
@@ -36235,7 +36241,7 @@
         <v>560</v>
       </c>
     </row>
-    <row r="233" spans="1:18" ht="14" hidden="1" x14ac:dyDescent="0.3">
+    <row r="233" spans="1:18" ht="14" x14ac:dyDescent="0.3">
       <c r="A233" s="2" t="s">
         <v>248</v>
       </c>
@@ -36254,14 +36260,14 @@
       </c>
       <c r="Q233" s="16"/>
     </row>
-    <row r="234" spans="1:18" ht="12.65" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="234" spans="1:18" ht="12.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A234" s="2" t="s">
         <v>319</v>
       </c>
       <c r="H234" s="12"/>
       <c r="I234" s="12"/>
     </row>
-    <row r="235" spans="1:18" ht="12.65" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="235" spans="1:18" ht="12.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A235" s="2" t="s">
         <v>252</v>
       </c>
@@ -36274,7 +36280,7 @@
         <v>328</v>
       </c>
     </row>
-    <row r="236" spans="1:18" ht="14" hidden="1" x14ac:dyDescent="0.3">
+    <row r="236" spans="1:18" ht="14" x14ac:dyDescent="0.3">
       <c r="A236" s="2" t="s">
         <v>248</v>
       </c>
@@ -36292,7 +36298,7 @@
       </c>
       <c r="Q236" s="16"/>
     </row>
-    <row r="237" spans="1:18" ht="14" hidden="1" x14ac:dyDescent="0.3">
+    <row r="237" spans="1:18" ht="14" x14ac:dyDescent="0.3">
       <c r="A237" s="2" t="s">
         <v>275</v>
       </c>
@@ -36316,7 +36322,7 @@
         <v>560</v>
       </c>
     </row>
-    <row r="238" spans="1:18" ht="14" hidden="1" x14ac:dyDescent="0.3">
+    <row r="238" spans="1:18" ht="14" x14ac:dyDescent="0.3">
       <c r="A238" s="2" t="s">
         <v>275</v>
       </c>
@@ -36340,7 +36346,7 @@
         <v>560</v>
       </c>
     </row>
-    <row r="239" spans="1:18" ht="14" hidden="1" x14ac:dyDescent="0.3">
+    <row r="239" spans="1:18" ht="14" x14ac:dyDescent="0.3">
       <c r="A239" s="2" t="s">
         <v>248</v>
       </c>
@@ -36359,14 +36365,14 @@
       </c>
       <c r="Q239" s="16"/>
     </row>
-    <row r="240" spans="1:18" ht="12.65" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="240" spans="1:18" ht="12.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A240" s="2" t="s">
         <v>319</v>
       </c>
       <c r="H240" s="12"/>
       <c r="I240" s="12"/>
     </row>
-    <row r="241" spans="1:18" ht="12.65" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="241" spans="1:18" ht="12.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A241" s="2" t="s">
         <v>252</v>
       </c>
@@ -36379,7 +36385,7 @@
         <v>328</v>
       </c>
     </row>
-    <row r="242" spans="1:18" ht="14" hidden="1" x14ac:dyDescent="0.3">
+    <row r="242" spans="1:18" ht="14" x14ac:dyDescent="0.3">
       <c r="A242" s="2" t="s">
         <v>248</v>
       </c>
@@ -36397,7 +36403,7 @@
       </c>
       <c r="Q242" s="16"/>
     </row>
-    <row r="243" spans="1:18" ht="14" hidden="1" x14ac:dyDescent="0.3">
+    <row r="243" spans="1:18" ht="14" x14ac:dyDescent="0.3">
       <c r="A243" s="2" t="s">
         <v>275</v>
       </c>
@@ -36421,7 +36427,7 @@
         <v>560</v>
       </c>
     </row>
-    <row r="244" spans="1:18" ht="14" hidden="1" x14ac:dyDescent="0.3">
+    <row r="244" spans="1:18" ht="14" x14ac:dyDescent="0.3">
       <c r="A244" s="2" t="s">
         <v>275</v>
       </c>
@@ -36445,7 +36451,7 @@
         <v>560</v>
       </c>
     </row>
-    <row r="245" spans="1:18" ht="14" hidden="1" x14ac:dyDescent="0.3">
+    <row r="245" spans="1:18" ht="14" x14ac:dyDescent="0.3">
       <c r="A245" s="2" t="s">
         <v>248</v>
       </c>
@@ -36464,14 +36470,14 @@
       </c>
       <c r="Q245" s="16"/>
     </row>
-    <row r="246" spans="1:18" ht="12.65" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="246" spans="1:18" ht="12.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A246" s="2" t="s">
         <v>319</v>
       </c>
       <c r="H246" s="12"/>
       <c r="I246" s="12"/>
     </row>
-    <row r="247" spans="1:18" ht="12.65" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="247" spans="1:18" ht="12.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A247" s="2" t="s">
         <v>252</v>
       </c>
@@ -36484,7 +36490,7 @@
         <v>328</v>
       </c>
     </row>
-    <row r="248" spans="1:18" ht="14" hidden="1" x14ac:dyDescent="0.3">
+    <row r="248" spans="1:18" ht="14" x14ac:dyDescent="0.3">
       <c r="A248" s="2" t="s">
         <v>248</v>
       </c>
@@ -36502,7 +36508,7 @@
       </c>
       <c r="Q248" s="16"/>
     </row>
-    <row r="249" spans="1:18" ht="14" hidden="1" x14ac:dyDescent="0.3">
+    <row r="249" spans="1:18" ht="14" x14ac:dyDescent="0.3">
       <c r="A249" s="2" t="s">
         <v>275</v>
       </c>
@@ -36526,7 +36532,7 @@
         <v>560</v>
       </c>
     </row>
-    <row r="250" spans="1:18" ht="14" hidden="1" x14ac:dyDescent="0.3">
+    <row r="250" spans="1:18" ht="14" x14ac:dyDescent="0.3">
       <c r="A250" s="2" t="s">
         <v>275</v>
       </c>
@@ -36550,7 +36556,7 @@
         <v>560</v>
       </c>
     </row>
-    <row r="251" spans="1:18" ht="14" hidden="1" x14ac:dyDescent="0.3">
+    <row r="251" spans="1:18" ht="14" x14ac:dyDescent="0.3">
       <c r="A251" s="2" t="s">
         <v>248</v>
       </c>
@@ -36569,14 +36575,14 @@
       </c>
       <c r="Q251" s="16"/>
     </row>
-    <row r="252" spans="1:18" ht="12.65" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="252" spans="1:18" ht="12.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A252" s="2" t="s">
         <v>319</v>
       </c>
       <c r="H252" s="12"/>
       <c r="I252" s="12"/>
     </row>
-    <row r="253" spans="1:18" ht="12.65" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="253" spans="1:18" ht="12.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A253" s="2" t="s">
         <v>252</v>
       </c>
@@ -36589,7 +36595,7 @@
         <v>328</v>
       </c>
     </row>
-    <row r="254" spans="1:18" ht="14" hidden="1" x14ac:dyDescent="0.3">
+    <row r="254" spans="1:18" ht="14" x14ac:dyDescent="0.3">
       <c r="A254" s="2" t="s">
         <v>248</v>
       </c>
@@ -36607,7 +36613,7 @@
       </c>
       <c r="Q254" s="16"/>
     </row>
-    <row r="255" spans="1:18" ht="14" hidden="1" x14ac:dyDescent="0.3">
+    <row r="255" spans="1:18" ht="14" x14ac:dyDescent="0.3">
       <c r="A255" s="2" t="s">
         <v>275</v>
       </c>
@@ -36631,7 +36637,7 @@
         <v>560</v>
       </c>
     </row>
-    <row r="256" spans="1:18" ht="14" hidden="1" x14ac:dyDescent="0.3">
+    <row r="256" spans="1:18" ht="14" x14ac:dyDescent="0.3">
       <c r="A256" s="2" t="s">
         <v>275</v>
       </c>
@@ -36655,7 +36661,7 @@
         <v>560</v>
       </c>
     </row>
-    <row r="257" spans="1:18" ht="14" hidden="1" x14ac:dyDescent="0.3">
+    <row r="257" spans="1:18" ht="14" x14ac:dyDescent="0.3">
       <c r="A257" s="2" t="s">
         <v>248</v>
       </c>
@@ -36674,14 +36680,14 @@
       </c>
       <c r="Q257" s="16"/>
     </row>
-    <row r="258" spans="1:18" ht="12.65" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="258" spans="1:18" ht="12.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A258" s="2" t="s">
         <v>319</v>
       </c>
       <c r="H258" s="12"/>
       <c r="I258" s="12"/>
     </row>
-    <row r="259" spans="1:18" ht="12.65" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="259" spans="1:18" ht="12.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A259" s="2" t="s">
         <v>252</v>
       </c>
@@ -36694,7 +36700,7 @@
         <v>328</v>
       </c>
     </row>
-    <row r="260" spans="1:18" ht="14" hidden="1" x14ac:dyDescent="0.3">
+    <row r="260" spans="1:18" ht="14" x14ac:dyDescent="0.3">
       <c r="A260" s="2" t="s">
         <v>248</v>
       </c>
@@ -36712,7 +36718,7 @@
       </c>
       <c r="Q260" s="16"/>
     </row>
-    <row r="261" spans="1:18" ht="14" hidden="1" x14ac:dyDescent="0.3">
+    <row r="261" spans="1:18" ht="14" x14ac:dyDescent="0.3">
       <c r="A261" s="2" t="s">
         <v>275</v>
       </c>
@@ -36736,7 +36742,7 @@
         <v>560</v>
       </c>
     </row>
-    <row r="262" spans="1:18" ht="14" hidden="1" x14ac:dyDescent="0.3">
+    <row r="262" spans="1:18" ht="14" x14ac:dyDescent="0.3">
       <c r="A262" s="2" t="s">
         <v>275</v>
       </c>
@@ -36760,7 +36766,7 @@
         <v>560</v>
       </c>
     </row>
-    <row r="263" spans="1:18" ht="14" hidden="1" x14ac:dyDescent="0.3">
+    <row r="263" spans="1:18" ht="14" x14ac:dyDescent="0.3">
       <c r="A263" s="2" t="s">
         <v>248</v>
       </c>
@@ -36779,14 +36785,14 @@
       </c>
       <c r="Q263" s="16"/>
     </row>
-    <row r="264" spans="1:18" ht="12.65" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="264" spans="1:18" ht="12.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A264" s="2" t="s">
         <v>319</v>
       </c>
       <c r="H264" s="12"/>
       <c r="I264" s="12"/>
     </row>
-    <row r="265" spans="1:18" ht="12.65" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="265" spans="1:18" ht="12.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A265" s="2" t="s">
         <v>252</v>
       </c>
@@ -36799,7 +36805,7 @@
         <v>328</v>
       </c>
     </row>
-    <row r="266" spans="1:18" ht="14" hidden="1" x14ac:dyDescent="0.3">
+    <row r="266" spans="1:18" ht="14" x14ac:dyDescent="0.3">
       <c r="A266" s="2" t="s">
         <v>248</v>
       </c>
@@ -36817,7 +36823,7 @@
       </c>
       <c r="Q266" s="16"/>
     </row>
-    <row r="267" spans="1:18" ht="14" hidden="1" x14ac:dyDescent="0.3">
+    <row r="267" spans="1:18" ht="14" x14ac:dyDescent="0.3">
       <c r="A267" s="2" t="s">
         <v>275</v>
       </c>
@@ -36841,7 +36847,7 @@
         <v>560</v>
       </c>
     </row>
-    <row r="268" spans="1:18" ht="14" hidden="1" x14ac:dyDescent="0.3">
+    <row r="268" spans="1:18" ht="14" x14ac:dyDescent="0.3">
       <c r="A268" s="2" t="s">
         <v>275</v>
       </c>
@@ -36868,7 +36874,7 @@
         <v>560</v>
       </c>
     </row>
-    <row r="269" spans="1:18" ht="14" hidden="1" x14ac:dyDescent="0.3">
+    <row r="269" spans="1:18" ht="14" x14ac:dyDescent="0.3">
       <c r="A269" s="2" t="s">
         <v>248</v>
       </c>
@@ -36887,14 +36893,14 @@
       </c>
       <c r="Q269" s="16"/>
     </row>
-    <row r="270" spans="1:18" ht="12.65" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="270" spans="1:18" ht="12.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A270" s="2" t="s">
         <v>319</v>
       </c>
       <c r="H270" s="12"/>
       <c r="I270" s="12"/>
     </row>
-    <row r="271" spans="1:18" ht="12.65" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="271" spans="1:18" ht="12.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A271" s="2" t="s">
         <v>252</v>
       </c>
@@ -36907,7 +36913,7 @@
         <v>328</v>
       </c>
     </row>
-    <row r="272" spans="1:18" ht="14" hidden="1" x14ac:dyDescent="0.3">
+    <row r="272" spans="1:18" ht="14" x14ac:dyDescent="0.3">
       <c r="A272" s="2" t="s">
         <v>248</v>
       </c>
@@ -36925,7 +36931,7 @@
       </c>
       <c r="Q272" s="16"/>
     </row>
-    <row r="273" spans="1:18" ht="14" hidden="1" x14ac:dyDescent="0.3">
+    <row r="273" spans="1:18" ht="14" x14ac:dyDescent="0.3">
       <c r="A273" s="2" t="s">
         <v>275</v>
       </c>
@@ -36949,7 +36955,7 @@
         <v>560</v>
       </c>
     </row>
-    <row r="274" spans="1:18" ht="14" hidden="1" x14ac:dyDescent="0.3">
+    <row r="274" spans="1:18" ht="14" x14ac:dyDescent="0.3">
       <c r="A274" s="2" t="s">
         <v>275</v>
       </c>
@@ -36976,7 +36982,7 @@
         <v>560</v>
       </c>
     </row>
-    <row r="275" spans="1:18" ht="14" hidden="1" x14ac:dyDescent="0.3">
+    <row r="275" spans="1:18" ht="14" x14ac:dyDescent="0.3">
       <c r="A275" s="2" t="s">
         <v>248</v>
       </c>
@@ -36995,14 +37001,14 @@
       </c>
       <c r="Q275" s="16"/>
     </row>
-    <row r="276" spans="1:18" ht="12.65" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="276" spans="1:18" ht="12.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A276" s="2" t="s">
         <v>319</v>
       </c>
       <c r="H276" s="12"/>
       <c r="I276" s="12"/>
     </row>
-    <row r="277" spans="1:18" ht="12.65" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="277" spans="1:18" ht="12.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A277" s="2" t="s">
         <v>252</v>
       </c>
@@ -37015,7 +37021,7 @@
         <v>328</v>
       </c>
     </row>
-    <row r="278" spans="1:18" ht="14" hidden="1" x14ac:dyDescent="0.3">
+    <row r="278" spans="1:18" ht="14" x14ac:dyDescent="0.3">
       <c r="A278" s="2" t="s">
         <v>248</v>
       </c>
@@ -37033,7 +37039,7 @@
       </c>
       <c r="Q278" s="16"/>
     </row>
-    <row r="279" spans="1:18" ht="14" hidden="1" x14ac:dyDescent="0.3">
+    <row r="279" spans="1:18" ht="14" x14ac:dyDescent="0.3">
       <c r="A279" s="2" t="s">
         <v>275</v>
       </c>
@@ -37057,7 +37063,7 @@
         <v>560</v>
       </c>
     </row>
-    <row r="280" spans="1:18" ht="14" hidden="1" x14ac:dyDescent="0.3">
+    <row r="280" spans="1:18" ht="14" x14ac:dyDescent="0.3">
       <c r="A280" s="2" t="s">
         <v>275</v>
       </c>
@@ -37084,7 +37090,7 @@
         <v>560</v>
       </c>
     </row>
-    <row r="281" spans="1:18" ht="14" hidden="1" x14ac:dyDescent="0.3">
+    <row r="281" spans="1:18" ht="14" x14ac:dyDescent="0.3">
       <c r="A281" s="2" t="s">
         <v>248</v>
       </c>
@@ -37103,14 +37109,14 @@
       </c>
       <c r="Q281" s="16"/>
     </row>
-    <row r="282" spans="1:18" ht="12.65" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="282" spans="1:18" ht="12.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A282" s="2" t="s">
         <v>319</v>
       </c>
       <c r="H282" s="12"/>
       <c r="I282" s="12"/>
     </row>
-    <row r="283" spans="1:18" ht="12.65" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="283" spans="1:18" ht="12.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A283" s="2" t="s">
         <v>252</v>
       </c>
@@ -37123,7 +37129,7 @@
         <v>328</v>
       </c>
     </row>
-    <row r="284" spans="1:18" ht="14" hidden="1" x14ac:dyDescent="0.3">
+    <row r="284" spans="1:18" ht="14" x14ac:dyDescent="0.3">
       <c r="A284" s="2" t="s">
         <v>248</v>
       </c>
@@ -37141,7 +37147,7 @@
       </c>
       <c r="Q284" s="16"/>
     </row>
-    <row r="285" spans="1:18" ht="14" hidden="1" x14ac:dyDescent="0.3">
+    <row r="285" spans="1:18" ht="14" x14ac:dyDescent="0.3">
       <c r="A285" s="2" t="s">
         <v>248</v>
       </c>
@@ -37160,7 +37166,7 @@
       </c>
       <c r="Q285"/>
     </row>
-    <row r="286" spans="1:18" ht="14" hidden="1" x14ac:dyDescent="0.3">
+    <row r="286" spans="1:18" ht="14" x14ac:dyDescent="0.3">
       <c r="A286" s="2" t="s">
         <v>248</v>
       </c>
@@ -37179,7 +37185,7 @@
       </c>
       <c r="Q286"/>
     </row>
-    <row r="287" spans="1:18" ht="14" hidden="1" x14ac:dyDescent="0.3">
+    <row r="287" spans="1:18" ht="14" x14ac:dyDescent="0.3">
       <c r="A287" s="2" t="s">
         <v>248</v>
       </c>
@@ -37198,18 +37204,18 @@
       </c>
       <c r="Q287" s="16"/>
     </row>
-    <row r="288" spans="1:18" ht="12.65" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="288" spans="1:18" ht="12.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A288" s="2" t="s">
         <v>319</v>
       </c>
       <c r="H288" s="12"/>
       <c r="I288" s="12"/>
     </row>
-    <row r="289" spans="1:18" ht="12.65" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="289" spans="1:18" ht="12.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="H289" s="12"/>
       <c r="I289" s="12"/>
     </row>
-    <row r="290" spans="1:18" s="33" customFormat="1" ht="13.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="290" spans="1:18" s="33" customFormat="1" ht="13.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A290" s="33" t="s">
         <v>517</v>
       </c>
@@ -37223,7 +37229,7 @@
         <v>748</v>
       </c>
     </row>
-    <row r="291" spans="1:18" s="33" customFormat="1" ht="13.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="291" spans="1:18" s="33" customFormat="1" ht="13.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A291" s="33" t="s">
         <v>517</v>
       </c>
@@ -37237,7 +37243,7 @@
         <v>750</v>
       </c>
     </row>
-    <row r="292" spans="1:18" s="33" customFormat="1" ht="13.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="292" spans="1:18" s="33" customFormat="1" ht="13.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A292" s="33" t="s">
         <v>517</v>
       </c>
@@ -37251,9 +37257,9 @@
         <v>752</v>
       </c>
     </row>
-    <row r="293" spans="1:18" s="35" customFormat="1" ht="13.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A293" s="64"/>
-      <c r="B293" s="65"/>
+    <row r="293" spans="1:18" s="35" customFormat="1" ht="13.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A293" s="65"/>
+      <c r="B293" s="66"/>
       <c r="C293" s="37"/>
       <c r="D293" s="37"/>
       <c r="E293" s="37"/>
@@ -37271,7 +37277,7 @@
       <c r="Q293" s="37"/>
       <c r="R293" s="38"/>
     </row>
-    <row r="294" spans="1:18" s="33" customFormat="1" ht="13.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="294" spans="1:18" s="33" customFormat="1" ht="13.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A294" s="33" t="s">
         <v>517</v>
       </c>
@@ -37285,7 +37291,7 @@
         <v>754</v>
       </c>
     </row>
-    <row r="295" spans="1:18" s="33" customFormat="1" ht="13.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="295" spans="1:18" s="33" customFormat="1" ht="13.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A295" s="33" t="s">
         <v>517</v>
       </c>
@@ -37299,7 +37305,7 @@
         <v>756</v>
       </c>
     </row>
-    <row r="296" spans="1:18" s="33" customFormat="1" ht="13.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="296" spans="1:18" s="33" customFormat="1" ht="13.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A296" s="33" t="s">
         <v>517</v>
       </c>
@@ -37313,7 +37319,7 @@
         <v>758</v>
       </c>
     </row>
-    <row r="297" spans="1:18" s="33" customFormat="1" ht="13.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="297" spans="1:18" s="33" customFormat="1" ht="13.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A297" s="33" t="s">
         <v>517</v>
       </c>
@@ -37327,7 +37333,7 @@
         <v>760</v>
       </c>
     </row>
-    <row r="298" spans="1:18" s="33" customFormat="1" ht="13.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="298" spans="1:18" s="33" customFormat="1" ht="13.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A298" s="33" t="s">
         <v>517</v>
       </c>
@@ -37341,7 +37347,7 @@
         <v>762</v>
       </c>
     </row>
-    <row r="299" spans="1:18" s="33" customFormat="1" ht="13.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="299" spans="1:18" s="33" customFormat="1" ht="13.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A299" s="33" t="s">
         <v>517</v>
       </c>
@@ -37355,7 +37361,7 @@
         <v>764</v>
       </c>
     </row>
-    <row r="300" spans="1:18" s="33" customFormat="1" ht="13.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="300" spans="1:18" s="33" customFormat="1" ht="13.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A300" s="33" t="s">
         <v>517</v>
       </c>
@@ -37369,7 +37375,7 @@
         <v>766</v>
       </c>
     </row>
-    <row r="301" spans="1:18" s="33" customFormat="1" ht="13.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="301" spans="1:18" s="33" customFormat="1" ht="13.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A301" s="33" t="s">
         <v>517</v>
       </c>
@@ -37383,7 +37389,7 @@
         <v>768</v>
       </c>
     </row>
-    <row r="302" spans="1:18" s="33" customFormat="1" ht="13.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="302" spans="1:18" s="33" customFormat="1" ht="13.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A302" s="33" t="s">
         <v>517</v>
       </c>
@@ -37397,7 +37403,7 @@
         <v>770</v>
       </c>
     </row>
-    <row r="303" spans="1:18" s="35" customFormat="1" ht="13.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="303" spans="1:18" s="35" customFormat="1" ht="13.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="O303" s="36"/>
     </row>
     <row r="304" spans="1:18" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
@@ -38861,7 +38867,7 @@
       <c r="Q382" s="8"/>
       <c r="R382" s="8"/>
     </row>
-    <row r="383" spans="1:18" ht="12.65" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="383" spans="1:18" ht="12.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A383" s="10" t="s">
         <v>322</v>
       </c>
@@ -38873,7 +38879,7 @@
         <v>557</v>
       </c>
     </row>
-    <row r="384" spans="1:18" ht="12.65" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="384" spans="1:18" ht="12.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A384" s="2" t="s">
         <v>252</v>
       </c>
@@ -38886,7 +38892,7 @@
         <v>328</v>
       </c>
     </row>
-    <row r="385" spans="1:18" ht="14" hidden="1" x14ac:dyDescent="0.3">
+    <row r="385" spans="1:18" ht="14" x14ac:dyDescent="0.3">
       <c r="A385" s="2" t="s">
         <v>248</v>
       </c>
@@ -38903,7 +38909,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="386" spans="1:18" ht="14" hidden="1" x14ac:dyDescent="0.3">
+    <row r="386" spans="1:18" ht="14" x14ac:dyDescent="0.3">
       <c r="A386" s="2" t="s">
         <v>248</v>
       </c>
@@ -38921,7 +38927,7 @@
       </c>
       <c r="Q386"/>
     </row>
-    <row r="387" spans="1:18" ht="14" hidden="1" x14ac:dyDescent="0.3">
+    <row r="387" spans="1:18" ht="14" x14ac:dyDescent="0.3">
       <c r="A387" s="2" t="s">
         <v>248</v>
       </c>
@@ -38939,7 +38945,7 @@
       </c>
       <c r="Q387"/>
     </row>
-    <row r="388" spans="1:18" ht="14" hidden="1" x14ac:dyDescent="0.3">
+    <row r="388" spans="1:18" ht="14" x14ac:dyDescent="0.3">
       <c r="A388" s="2" t="s">
         <v>248</v>
       </c>
@@ -38956,17 +38962,17 @@
         <v>259</v>
       </c>
     </row>
-    <row r="389" spans="1:18" ht="12.65" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="389" spans="1:18" ht="12.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A389" s="2" t="s">
         <v>319</v>
       </c>
       <c r="H389" s="12"/>
       <c r="I389" s="12"/>
     </row>
-    <row r="390" spans="1:18" ht="14" hidden="1" x14ac:dyDescent="0.3">
+    <row r="390" spans="1:18" ht="14" x14ac:dyDescent="0.3">
       <c r="H390" s="2"/>
     </row>
-    <row r="391" spans="1:18" ht="12.65" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="391" spans="1:18" ht="12.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A391" s="2" t="s">
         <v>252</v>
       </c>
@@ -38979,7 +38985,7 @@
         <v>328</v>
       </c>
     </row>
-    <row r="392" spans="1:18" ht="14" hidden="1" x14ac:dyDescent="0.3">
+    <row r="392" spans="1:18" ht="14" x14ac:dyDescent="0.3">
       <c r="A392" s="2" t="s">
         <v>248</v>
       </c>
@@ -38997,7 +39003,7 @@
       </c>
       <c r="Q392" s="16"/>
     </row>
-    <row r="393" spans="1:18" ht="14" hidden="1" x14ac:dyDescent="0.3">
+    <row r="393" spans="1:18" ht="14" x14ac:dyDescent="0.3">
       <c r="A393" s="2" t="s">
         <v>275</v>
       </c>
@@ -39021,7 +39027,7 @@
         <v>560</v>
       </c>
     </row>
-    <row r="394" spans="1:18" ht="14" hidden="1" x14ac:dyDescent="0.3">
+    <row r="394" spans="1:18" ht="14" x14ac:dyDescent="0.3">
       <c r="A394" s="2" t="s">
         <v>275</v>
       </c>
@@ -39045,7 +39051,7 @@
         <v>560</v>
       </c>
     </row>
-    <row r="395" spans="1:18" ht="14" hidden="1" x14ac:dyDescent="0.3">
+    <row r="395" spans="1:18" ht="14" x14ac:dyDescent="0.3">
       <c r="A395" s="2" t="s">
         <v>248</v>
       </c>
@@ -39064,14 +39070,14 @@
       </c>
       <c r="Q395" s="16"/>
     </row>
-    <row r="396" spans="1:18" ht="12.65" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="396" spans="1:18" ht="12.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A396" s="2" t="s">
         <v>319</v>
       </c>
       <c r="H396" s="12"/>
       <c r="I396" s="12"/>
     </row>
-    <row r="397" spans="1:18" ht="12.65" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="397" spans="1:18" ht="12.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A397" s="2" t="s">
         <v>252</v>
       </c>
@@ -39084,7 +39090,7 @@
         <v>328</v>
       </c>
     </row>
-    <row r="398" spans="1:18" ht="14" hidden="1" x14ac:dyDescent="0.3">
+    <row r="398" spans="1:18" ht="14" x14ac:dyDescent="0.3">
       <c r="A398" s="2" t="s">
         <v>248</v>
       </c>
@@ -39102,7 +39108,7 @@
       </c>
       <c r="Q398" s="16"/>
     </row>
-    <row r="399" spans="1:18" ht="14" hidden="1" x14ac:dyDescent="0.3">
+    <row r="399" spans="1:18" ht="14" x14ac:dyDescent="0.3">
       <c r="A399" s="2" t="s">
         <v>275</v>
       </c>
@@ -39126,7 +39132,7 @@
         <v>560</v>
       </c>
     </row>
-    <row r="400" spans="1:18" ht="14" hidden="1" x14ac:dyDescent="0.3">
+    <row r="400" spans="1:18" ht="14" x14ac:dyDescent="0.3">
       <c r="A400" s="2" t="s">
         <v>275</v>
       </c>
@@ -39150,7 +39156,7 @@
         <v>560</v>
       </c>
     </row>
-    <row r="401" spans="1:18" ht="14" hidden="1" x14ac:dyDescent="0.3">
+    <row r="401" spans="1:18" ht="14" x14ac:dyDescent="0.3">
       <c r="A401" s="2" t="s">
         <v>248</v>
       </c>
@@ -39169,14 +39175,14 @@
       </c>
       <c r="Q401" s="16"/>
     </row>
-    <row r="402" spans="1:18" ht="12.65" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="402" spans="1:18" ht="12.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A402" s="2" t="s">
         <v>319</v>
       </c>
       <c r="H402" s="12"/>
       <c r="I402" s="12"/>
     </row>
-    <row r="403" spans="1:18" ht="12.65" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="403" spans="1:18" ht="12.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A403" s="2" t="s">
         <v>252</v>
       </c>
@@ -39189,7 +39195,7 @@
         <v>328</v>
       </c>
     </row>
-    <row r="404" spans="1:18" ht="14" hidden="1" x14ac:dyDescent="0.3">
+    <row r="404" spans="1:18" ht="14" x14ac:dyDescent="0.3">
       <c r="A404" s="2" t="s">
         <v>248</v>
       </c>
@@ -39207,7 +39213,7 @@
       </c>
       <c r="Q404" s="16"/>
     </row>
-    <row r="405" spans="1:18" ht="14" hidden="1" x14ac:dyDescent="0.3">
+    <row r="405" spans="1:18" ht="14" x14ac:dyDescent="0.3">
       <c r="A405" s="2" t="s">
         <v>275</v>
       </c>
@@ -39231,7 +39237,7 @@
         <v>560</v>
       </c>
     </row>
-    <row r="406" spans="1:18" ht="14" hidden="1" x14ac:dyDescent="0.3">
+    <row r="406" spans="1:18" ht="14" x14ac:dyDescent="0.3">
       <c r="A406" s="2" t="s">
         <v>275</v>
       </c>
@@ -39255,7 +39261,7 @@
         <v>560</v>
       </c>
     </row>
-    <row r="407" spans="1:18" ht="14" hidden="1" x14ac:dyDescent="0.3">
+    <row r="407" spans="1:18" ht="14" x14ac:dyDescent="0.3">
       <c r="A407" s="2" t="s">
         <v>248</v>
       </c>
@@ -39274,14 +39280,14 @@
       </c>
       <c r="Q407" s="16"/>
     </row>
-    <row r="408" spans="1:18" ht="12.65" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="408" spans="1:18" ht="12.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A408" s="2" t="s">
         <v>319</v>
       </c>
       <c r="H408" s="12"/>
       <c r="I408" s="12"/>
     </row>
-    <row r="409" spans="1:18" ht="12.65" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="409" spans="1:18" ht="12.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A409" s="2" t="s">
         <v>252</v>
       </c>
@@ -39294,7 +39300,7 @@
         <v>328</v>
       </c>
     </row>
-    <row r="410" spans="1:18" ht="14" hidden="1" x14ac:dyDescent="0.3">
+    <row r="410" spans="1:18" ht="14" x14ac:dyDescent="0.3">
       <c r="A410" s="2" t="s">
         <v>248</v>
       </c>
@@ -39312,7 +39318,7 @@
       </c>
       <c r="Q410" s="16"/>
     </row>
-    <row r="411" spans="1:18" ht="14" hidden="1" x14ac:dyDescent="0.3">
+    <row r="411" spans="1:18" ht="14" x14ac:dyDescent="0.3">
       <c r="A411" s="2" t="s">
         <v>275</v>
       </c>
@@ -39336,7 +39342,7 @@
         <v>560</v>
       </c>
     </row>
-    <row r="412" spans="1:18" ht="14" hidden="1" x14ac:dyDescent="0.3">
+    <row r="412" spans="1:18" ht="14" x14ac:dyDescent="0.3">
       <c r="A412" s="2" t="s">
         <v>275</v>
       </c>
@@ -39360,7 +39366,7 @@
         <v>560</v>
       </c>
     </row>
-    <row r="413" spans="1:18" ht="14" hidden="1" x14ac:dyDescent="0.3">
+    <row r="413" spans="1:18" ht="14" x14ac:dyDescent="0.3">
       <c r="A413" s="2" t="s">
         <v>248</v>
       </c>
@@ -39379,14 +39385,14 @@
       </c>
       <c r="Q413" s="16"/>
     </row>
-    <row r="414" spans="1:18" ht="12.65" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="414" spans="1:18" ht="12.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A414" s="2" t="s">
         <v>319</v>
       </c>
       <c r="H414" s="12"/>
       <c r="I414" s="12"/>
     </row>
-    <row r="415" spans="1:18" ht="12.65" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="415" spans="1:18" ht="12.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A415" s="2" t="s">
         <v>252</v>
       </c>
@@ -39399,7 +39405,7 @@
         <v>328</v>
       </c>
     </row>
-    <row r="416" spans="1:18" ht="14" hidden="1" x14ac:dyDescent="0.3">
+    <row r="416" spans="1:18" ht="14" x14ac:dyDescent="0.3">
       <c r="A416" s="2" t="s">
         <v>248</v>
       </c>
@@ -39417,7 +39423,7 @@
       </c>
       <c r="Q416" s="16"/>
     </row>
-    <row r="417" spans="1:18" ht="14" hidden="1" x14ac:dyDescent="0.3">
+    <row r="417" spans="1:18" ht="14" x14ac:dyDescent="0.3">
       <c r="A417" s="2" t="s">
         <v>248</v>
       </c>
@@ -39436,7 +39442,7 @@
       </c>
       <c r="Q417"/>
     </row>
-    <row r="418" spans="1:18" ht="14" hidden="1" x14ac:dyDescent="0.3">
+    <row r="418" spans="1:18" ht="14" x14ac:dyDescent="0.3">
       <c r="A418" s="2" t="s">
         <v>248</v>
       </c>
@@ -39455,7 +39461,7 @@
       </c>
       <c r="Q418"/>
     </row>
-    <row r="419" spans="1:18" ht="14" hidden="1" x14ac:dyDescent="0.3">
+    <row r="419" spans="1:18" ht="14" x14ac:dyDescent="0.3">
       <c r="A419" s="2" t="s">
         <v>248</v>
       </c>
@@ -39474,18 +39480,18 @@
       </c>
       <c r="Q419" s="16"/>
     </row>
-    <row r="420" spans="1:18" ht="12.65" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="420" spans="1:18" ht="12.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A420" s="2" t="s">
         <v>319</v>
       </c>
       <c r="H420" s="12"/>
       <c r="I420" s="12"/>
     </row>
-    <row r="421" spans="1:18" ht="12.65" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="421" spans="1:18" ht="12.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="H421" s="12"/>
       <c r="I421" s="12"/>
     </row>
-    <row r="422" spans="1:18" s="33" customFormat="1" ht="13.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="422" spans="1:18" s="33" customFormat="1" ht="13.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A422" s="33" t="s">
         <v>517</v>
       </c>
@@ -39499,7 +39505,7 @@
         <v>852</v>
       </c>
     </row>
-    <row r="423" spans="1:18" s="33" customFormat="1" ht="13.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="423" spans="1:18" s="33" customFormat="1" ht="13.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A423" s="33" t="s">
         <v>517</v>
       </c>
@@ -39513,7 +39519,7 @@
         <v>853</v>
       </c>
     </row>
-    <row r="424" spans="1:18" s="33" customFormat="1" ht="13.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="424" spans="1:18" s="33" customFormat="1" ht="13.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A424" s="33" t="s">
         <v>517</v>
       </c>
@@ -39527,9 +39533,9 @@
         <v>837</v>
       </c>
     </row>
-    <row r="425" spans="1:18" s="35" customFormat="1" ht="13.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A425" s="64"/>
-      <c r="B425" s="65"/>
+    <row r="425" spans="1:18" s="35" customFormat="1" ht="13.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A425" s="65"/>
+      <c r="B425" s="66"/>
       <c r="C425" s="37"/>
       <c r="D425" s="37"/>
       <c r="E425" s="37"/>
@@ -39547,7 +39553,7 @@
       <c r="Q425" s="37"/>
       <c r="R425" s="38"/>
     </row>
-    <row r="426" spans="1:18" s="33" customFormat="1" ht="13.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="426" spans="1:18" s="33" customFormat="1" ht="13.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A426" s="33" t="s">
         <v>517</v>
       </c>
@@ -39561,7 +39567,7 @@
         <v>839</v>
       </c>
     </row>
-    <row r="427" spans="1:18" s="33" customFormat="1" ht="13.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="427" spans="1:18" s="33" customFormat="1" ht="13.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A427" s="33" t="s">
         <v>517</v>
       </c>
@@ -39575,7 +39581,7 @@
         <v>841</v>
       </c>
     </row>
-    <row r="428" spans="1:18" s="33" customFormat="1" ht="13.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="428" spans="1:18" s="33" customFormat="1" ht="13.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A428" s="33" t="s">
         <v>517</v>
       </c>
@@ -39589,7 +39595,7 @@
         <v>843</v>
       </c>
     </row>
-    <row r="429" spans="1:18" s="33" customFormat="1" ht="13.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="429" spans="1:18" s="33" customFormat="1" ht="13.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A429" s="33" t="s">
         <v>517</v>
       </c>
@@ -39603,10 +39609,10 @@
         <v>845</v>
       </c>
     </row>
-    <row r="430" spans="1:18" s="35" customFormat="1" ht="13.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="430" spans="1:18" s="35" customFormat="1" ht="13.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="O430" s="36"/>
     </row>
-    <row r="431" spans="1:18" s="33" customFormat="1" ht="13.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="431" spans="1:18" s="33" customFormat="1" ht="13.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A431" s="33" t="s">
         <v>248</v>
       </c>
@@ -39627,7 +39633,7 @@
       </c>
       <c r="O431" s="34"/>
     </row>
-    <row r="432" spans="1:18" s="33" customFormat="1" ht="13.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="432" spans="1:18" s="33" customFormat="1" ht="13.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A432" s="33" t="s">
         <v>248</v>
       </c>
@@ -40473,8 +40479,8 @@
       </c>
     </row>
     <row r="484" spans="1:18" s="35" customFormat="1" ht="13.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A484" s="64"/>
-      <c r="B484" s="65"/>
+      <c r="A484" s="65"/>
+      <c r="B484" s="66"/>
       <c r="C484" s="37"/>
       <c r="D484" s="37"/>
       <c r="E484" s="37"/>
@@ -40659,7 +40665,7 @@
       <c r="Q495" s="8"/>
       <c r="R495" s="8"/>
     </row>
-    <row r="496" spans="1:18" ht="14" hidden="1" x14ac:dyDescent="0.3">
+    <row r="496" spans="1:18" ht="14" x14ac:dyDescent="0.3">
       <c r="A496" s="10" t="s">
         <v>322</v>
       </c>
@@ -40672,7 +40678,7 @@
       </c>
       <c r="O496" s="16"/>
     </row>
-    <row r="497" spans="1:18" ht="14" hidden="1" x14ac:dyDescent="0.3">
+    <row r="497" spans="1:18" ht="14" x14ac:dyDescent="0.3">
       <c r="A497" s="2" t="s">
         <v>252</v>
       </c>
@@ -40686,7 +40692,7 @@
       </c>
       <c r="O497" s="16"/>
     </row>
-    <row r="498" spans="1:18" ht="14" hidden="1" x14ac:dyDescent="0.3">
+    <row r="498" spans="1:18" ht="14" x14ac:dyDescent="0.3">
       <c r="A498" s="2" t="s">
         <v>248</v>
       </c>
@@ -40704,7 +40710,7 @@
       </c>
       <c r="O498" s="16"/>
     </row>
-    <row r="499" spans="1:18" ht="14" hidden="1" x14ac:dyDescent="0.3">
+    <row r="499" spans="1:18" ht="14" x14ac:dyDescent="0.3">
       <c r="A499" s="2" t="s">
         <v>248</v>
       </c>
@@ -40722,7 +40728,7 @@
       </c>
       <c r="O499" s="16"/>
     </row>
-    <row r="500" spans="1:18" ht="14" hidden="1" x14ac:dyDescent="0.3">
+    <row r="500" spans="1:18" ht="14" x14ac:dyDescent="0.3">
       <c r="A500" s="2" t="s">
         <v>248</v>
       </c>
@@ -40740,7 +40746,7 @@
       </c>
       <c r="O500" s="16"/>
     </row>
-    <row r="501" spans="1:18" ht="14" hidden="1" x14ac:dyDescent="0.3">
+    <row r="501" spans="1:18" ht="14" x14ac:dyDescent="0.3">
       <c r="A501" s="2" t="s">
         <v>275</v>
       </c>
@@ -40770,7 +40776,7 @@
         <v>560</v>
       </c>
     </row>
-    <row r="502" spans="1:18" ht="14" hidden="1" x14ac:dyDescent="0.3">
+    <row r="502" spans="1:18" ht="14" x14ac:dyDescent="0.3">
       <c r="A502" s="2" t="s">
         <v>248</v>
       </c>
@@ -40788,7 +40794,7 @@
       </c>
       <c r="O502" s="16"/>
     </row>
-    <row r="503" spans="1:18" ht="14" hidden="1" x14ac:dyDescent="0.3">
+    <row r="503" spans="1:18" ht="14" x14ac:dyDescent="0.3">
       <c r="A503" s="2" t="s">
         <v>275</v>
       </c>
@@ -40818,7 +40824,7 @@
         <v>560</v>
       </c>
     </row>
-    <row r="504" spans="1:18" ht="14" hidden="1" x14ac:dyDescent="0.3">
+    <row r="504" spans="1:18" ht="14" x14ac:dyDescent="0.3">
       <c r="A504" s="2" t="s">
         <v>248</v>
       </c>
@@ -40836,7 +40842,7 @@
       </c>
       <c r="O504" s="16"/>
     </row>
-    <row r="505" spans="1:18" ht="14" hidden="1" x14ac:dyDescent="0.3">
+    <row r="505" spans="1:18" ht="14" x14ac:dyDescent="0.3">
       <c r="A505" s="2" t="s">
         <v>517</v>
       </c>
@@ -40857,7 +40863,7 @@
       </c>
       <c r="Q505"/>
     </row>
-    <row r="506" spans="1:18" ht="14" hidden="1" x14ac:dyDescent="0.3">
+    <row r="506" spans="1:18" ht="14" x14ac:dyDescent="0.3">
       <c r="A506" s="2" t="s">
         <v>248</v>
       </c>
@@ -40873,7 +40879,7 @@
       <c r="O506" s="16"/>
       <c r="Q506"/>
     </row>
-    <row r="507" spans="1:18" ht="14" hidden="1" x14ac:dyDescent="0.3">
+    <row r="507" spans="1:18" ht="14" x14ac:dyDescent="0.3">
       <c r="A507" s="2" t="s">
         <v>319</v>
       </c>
@@ -41568,8 +41574,8 @@
       </c>
     </row>
     <row r="548" spans="1:18" s="35" customFormat="1" ht="13.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A548" s="64"/>
-      <c r="B548" s="65"/>
+      <c r="A548" s="65"/>
+      <c r="B548" s="66"/>
       <c r="C548" s="37"/>
       <c r="D548" s="37"/>
       <c r="E548" s="37"/>
@@ -44597,7 +44603,7 @@
       <c r="Q692" s="6"/>
       <c r="R692" s="6"/>
     </row>
-    <row r="693" spans="1:18" ht="14" hidden="1" x14ac:dyDescent="0.3">
+    <row r="693" spans="1:18" ht="14" x14ac:dyDescent="0.3">
       <c r="A693" s="19" t="s">
         <v>322</v>
       </c>
@@ -44611,7 +44617,7 @@
       <c r="N693" s="15"/>
       <c r="O693" s="15"/>
     </row>
-    <row r="694" spans="1:18" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="694" spans="1:18" ht="12" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A694" s="12" t="s">
         <v>481</v>
       </c>
@@ -44636,7 +44642,7 @@
       <c r="N694" s="15"/>
       <c r="O694" s="15"/>
     </row>
-    <row r="695" spans="1:18" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="695" spans="1:18" ht="12" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A695" s="12" t="s">
         <v>486</v>
       </c>
@@ -44663,7 +44669,7 @@
       </c>
       <c r="O695" s="15"/>
     </row>
-    <row r="696" spans="1:18" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="696" spans="1:18" ht="12" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A696" s="12" t="s">
         <v>491</v>
       </c>
@@ -44690,7 +44696,7 @@
       </c>
       <c r="O696" s="15"/>
     </row>
-    <row r="697" spans="1:18" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="697" spans="1:18" ht="12" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A697" s="12" t="s">
         <v>248</v>
       </c>
@@ -44712,7 +44718,7 @@
       </c>
       <c r="O697" s="15"/>
     </row>
-    <row r="698" spans="1:18" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="698" spans="1:18" ht="12" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A698" s="12" t="s">
         <v>270</v>
       </c>
@@ -44739,7 +44745,7 @@
       </c>
       <c r="O698" s="15"/>
     </row>
-    <row r="699" spans="1:18" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="699" spans="1:18" ht="12" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A699" s="12" t="s">
         <v>270</v>
       </c>
@@ -44766,7 +44772,7 @@
       </c>
       <c r="O699" s="15"/>
     </row>
-    <row r="700" spans="1:18" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="700" spans="1:18" ht="12" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A700" s="12" t="s">
         <v>270</v>
       </c>

--- a/XLS/S3/s3.xlsx
+++ b/XLS/S3/s3.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Mohammed Al-Emara\Documents\GitHub\Statistical-notebook\XLS\S3\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FCCF54F1-DED8-41AD-9060-114CA932DA87}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F36FBF3B-D683-4E4A-92FF-2177CC6EEAB1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" tabRatio="500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="choices" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6664" uniqueCount="2566">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6664" uniqueCount="2565">
   <si>
     <t>list_name</t>
   </si>
@@ -6168,9 +6168,6 @@
   </si>
   <si>
     <t>حي الزوية</t>
-  </si>
-  <si>
-    <t>حي الشاي</t>
   </si>
   <si>
     <t>حي الزهور</t>
@@ -8480,10 +8477,10 @@
         <v>3</v>
       </c>
       <c r="C6" s="48" t="s">
-        <v>2562</v>
+        <v>2561</v>
       </c>
       <c r="D6" s="48" t="s">
-        <v>2562</v>
+        <v>2561</v>
       </c>
       <c r="I6" s="49"/>
     </row>
@@ -8572,10 +8569,10 @@
         <v>3</v>
       </c>
       <c r="C12" t="s">
-        <v>2562</v>
+        <v>2561</v>
       </c>
       <c r="D12" t="s">
-        <v>2562</v>
+        <v>2561</v>
       </c>
       <c r="E12">
         <v>3</v>
@@ -8978,10 +8975,10 @@
         <v>3</v>
       </c>
       <c r="C38" t="s">
-        <v>2491</v>
+        <v>2490</v>
       </c>
       <c r="D38" t="s">
-        <v>2491</v>
+        <v>2490</v>
       </c>
     </row>
     <row r="39" spans="1:4" ht="14" x14ac:dyDescent="0.3">
@@ -11647,7 +11644,7 @@
         <v>280002</v>
       </c>
       <c r="C222" t="s">
-        <v>2479</v>
+        <v>2478</v>
       </c>
       <c r="G222">
         <v>1</v>
@@ -11681,7 +11678,7 @@
         <v>280004</v>
       </c>
       <c r="C224" t="s">
-        <v>2480</v>
+        <v>2479</v>
       </c>
       <c r="G224">
         <v>1</v>
@@ -11698,7 +11695,7 @@
         <v>280005</v>
       </c>
       <c r="C225" t="s">
-        <v>2481</v>
+        <v>2480</v>
       </c>
       <c r="G225">
         <v>1</v>
@@ -11732,7 +11729,7 @@
         <v>280007</v>
       </c>
       <c r="C227" t="s">
-        <v>2482</v>
+        <v>2481</v>
       </c>
       <c r="G227">
         <v>1</v>
@@ -11749,7 +11746,7 @@
         <v>280008</v>
       </c>
       <c r="C228" t="s">
-        <v>2483</v>
+        <v>2482</v>
       </c>
       <c r="G228">
         <v>1</v>
@@ -12344,7 +12341,7 @@
         <v>280058</v>
       </c>
       <c r="C263" s="62" t="s">
-        <v>2484</v>
+        <v>2483</v>
       </c>
       <c r="G263">
         <v>1</v>
@@ -15965,7 +15962,7 @@
         <v>281014</v>
       </c>
       <c r="C476" t="s">
-        <v>2557</v>
+        <v>2556</v>
       </c>
       <c r="G476">
         <v>7</v>
@@ -15982,7 +15979,7 @@
         <v>281015</v>
       </c>
       <c r="C477" t="s">
-        <v>2558</v>
+        <v>2557</v>
       </c>
       <c r="G477">
         <v>7</v>
@@ -16679,7 +16676,7 @@
         <v>281220</v>
       </c>
       <c r="C518" t="s">
-        <v>2028</v>
+        <v>1734</v>
       </c>
       <c r="G518">
         <v>9</v>
@@ -16696,7 +16693,7 @@
         <v>281221</v>
       </c>
       <c r="C519" t="s">
-        <v>2029</v>
+        <v>2028</v>
       </c>
       <c r="G519">
         <v>9</v>
@@ -16713,7 +16710,7 @@
         <v>281222</v>
       </c>
       <c r="C520" t="s">
-        <v>2035</v>
+        <v>2034</v>
       </c>
       <c r="G520">
         <v>9</v>
@@ -16730,7 +16727,7 @@
         <v>281223</v>
       </c>
       <c r="C521" t="s">
-        <v>2030</v>
+        <v>2029</v>
       </c>
       <c r="G521">
         <v>9</v>
@@ -16747,7 +16744,7 @@
         <v>281224</v>
       </c>
       <c r="C522" t="s">
-        <v>2031</v>
+        <v>2030</v>
       </c>
       <c r="G522">
         <v>9</v>
@@ -16781,7 +16778,7 @@
         <v>281226</v>
       </c>
       <c r="C524" t="s">
-        <v>2032</v>
+        <v>2031</v>
       </c>
       <c r="G524">
         <v>9</v>
@@ -16815,7 +16812,7 @@
         <v>281229</v>
       </c>
       <c r="C526" t="s">
-        <v>2033</v>
+        <v>2032</v>
       </c>
       <c r="G526">
         <v>9</v>
@@ -16866,7 +16863,7 @@
         <v>281232</v>
       </c>
       <c r="C529" t="s">
-        <v>2034</v>
+        <v>2033</v>
       </c>
       <c r="G529">
         <v>9</v>
@@ -16883,7 +16880,7 @@
         <v>281233</v>
       </c>
       <c r="C530" t="s">
-        <v>2036</v>
+        <v>2035</v>
       </c>
       <c r="G530">
         <v>9</v>
@@ -16917,7 +16914,7 @@
         <v>281235</v>
       </c>
       <c r="C532" t="s">
-        <v>2037</v>
+        <v>2036</v>
       </c>
       <c r="G532">
         <v>9</v>
@@ -16934,7 +16931,7 @@
         <v>281236</v>
       </c>
       <c r="C533" t="s">
-        <v>2038</v>
+        <v>2037</v>
       </c>
       <c r="G533">
         <v>9</v>
@@ -16951,7 +16948,7 @@
         <v>281237</v>
       </c>
       <c r="C534" t="s">
-        <v>2039</v>
+        <v>2038</v>
       </c>
       <c r="G534">
         <v>9</v>
@@ -16968,7 +16965,7 @@
         <v>281238</v>
       </c>
       <c r="C535" t="s">
-        <v>2559</v>
+        <v>2558</v>
       </c>
       <c r="G535">
         <v>9</v>
@@ -16985,7 +16982,7 @@
         <v>281239</v>
       </c>
       <c r="C536" t="s">
-        <v>2040</v>
+        <v>2039</v>
       </c>
       <c r="G536">
         <v>9</v>
@@ -17002,7 +16999,7 @@
         <v>281240</v>
       </c>
       <c r="C537" t="s">
-        <v>2041</v>
+        <v>2040</v>
       </c>
       <c r="G537">
         <v>9</v>
@@ -17019,7 +17016,7 @@
         <v>281241</v>
       </c>
       <c r="C538" t="s">
-        <v>2560</v>
+        <v>2559</v>
       </c>
       <c r="G538">
         <v>9</v>
@@ -17036,7 +17033,7 @@
         <v>281242</v>
       </c>
       <c r="C539" t="s">
-        <v>2042</v>
+        <v>2041</v>
       </c>
       <c r="G539">
         <v>9</v>
@@ -17053,7 +17050,7 @@
         <v>281243</v>
       </c>
       <c r="C540" t="s">
-        <v>2043</v>
+        <v>2042</v>
       </c>
       <c r="G540">
         <v>9</v>
@@ -17070,7 +17067,7 @@
         <v>281244</v>
       </c>
       <c r="C541" t="s">
-        <v>2044</v>
+        <v>2043</v>
       </c>
       <c r="G541">
         <v>9</v>
@@ -17104,7 +17101,7 @@
         <v>281246</v>
       </c>
       <c r="C543" t="s">
-        <v>2045</v>
+        <v>2044</v>
       </c>
       <c r="G543">
         <v>9</v>
@@ -17138,7 +17135,7 @@
         <v>281248</v>
       </c>
       <c r="C545" t="s">
-        <v>2046</v>
+        <v>2045</v>
       </c>
       <c r="G545">
         <v>9</v>
@@ -17155,7 +17152,7 @@
         <v>281249</v>
       </c>
       <c r="C546" t="s">
-        <v>2047</v>
+        <v>2046</v>
       </c>
       <c r="G546">
         <v>9</v>
@@ -17189,7 +17186,7 @@
         <v>281300</v>
       </c>
       <c r="C548" t="s">
-        <v>2077</v>
+        <v>2076</v>
       </c>
       <c r="G548">
         <v>9</v>
@@ -17206,7 +17203,7 @@
         <v>281301</v>
       </c>
       <c r="C549" t="s">
-        <v>2078</v>
+        <v>2077</v>
       </c>
       <c r="G549">
         <v>9</v>
@@ -17223,7 +17220,7 @@
         <v>281302</v>
       </c>
       <c r="C550" t="s">
-        <v>2079</v>
+        <v>2078</v>
       </c>
       <c r="G550">
         <v>9</v>
@@ -17240,7 +17237,7 @@
         <v>281309</v>
       </c>
       <c r="C551" t="s">
-        <v>2080</v>
+        <v>2079</v>
       </c>
       <c r="G551">
         <v>9</v>
@@ -17257,7 +17254,7 @@
         <v>281311</v>
       </c>
       <c r="C552" t="s">
-        <v>2049</v>
+        <v>2048</v>
       </c>
       <c r="G552">
         <v>9</v>
@@ -17274,7 +17271,7 @@
         <v>281313</v>
       </c>
       <c r="C553" t="s">
-        <v>2081</v>
+        <v>2080</v>
       </c>
       <c r="G553">
         <v>9</v>
@@ -17291,7 +17288,7 @@
         <v>281314</v>
       </c>
       <c r="C554" t="s">
-        <v>2082</v>
+        <v>2081</v>
       </c>
       <c r="G554">
         <v>9</v>
@@ -17308,7 +17305,7 @@
         <v>281315</v>
       </c>
       <c r="C555" t="s">
-        <v>2083</v>
+        <v>2082</v>
       </c>
       <c r="G555">
         <v>9</v>
@@ -17325,7 +17322,7 @@
         <v>281316</v>
       </c>
       <c r="C556" t="s">
-        <v>2084</v>
+        <v>2083</v>
       </c>
       <c r="G556">
         <v>9</v>
@@ -17342,7 +17339,7 @@
         <v>281322</v>
       </c>
       <c r="C557" t="s">
-        <v>2085</v>
+        <v>2084</v>
       </c>
       <c r="G557">
         <v>9</v>
@@ -17359,7 +17356,7 @@
         <v>281323</v>
       </c>
       <c r="C558" t="s">
-        <v>2050</v>
+        <v>2049</v>
       </c>
       <c r="G558">
         <v>9</v>
@@ -17376,7 +17373,7 @@
         <v>281324</v>
       </c>
       <c r="C559" t="s">
-        <v>2051</v>
+        <v>2050</v>
       </c>
       <c r="G559">
         <v>9</v>
@@ -17393,7 +17390,7 @@
         <v>281326</v>
       </c>
       <c r="C560" t="s">
-        <v>2086</v>
+        <v>2085</v>
       </c>
       <c r="G560">
         <v>9</v>
@@ -17410,7 +17407,7 @@
         <v>281376</v>
       </c>
       <c r="C561" t="s">
-        <v>2087</v>
+        <v>2086</v>
       </c>
       <c r="G561">
         <v>10</v>
@@ -17427,7 +17424,7 @@
         <v>281377</v>
       </c>
       <c r="C562" t="s">
-        <v>2088</v>
+        <v>2087</v>
       </c>
       <c r="G562">
         <v>10</v>
@@ -17444,7 +17441,7 @@
         <v>281378</v>
       </c>
       <c r="C563" t="s">
-        <v>2089</v>
+        <v>2088</v>
       </c>
       <c r="G563">
         <v>10</v>
@@ -17478,7 +17475,7 @@
         <v>281380</v>
       </c>
       <c r="C565" t="s">
-        <v>2090</v>
+        <v>2089</v>
       </c>
       <c r="G565">
         <v>10</v>
@@ -17495,7 +17492,7 @@
         <v>281381</v>
       </c>
       <c r="C566" t="s">
-        <v>2091</v>
+        <v>2090</v>
       </c>
       <c r="G566">
         <v>10</v>
@@ -17563,7 +17560,7 @@
         <v>281385</v>
       </c>
       <c r="C570" t="s">
-        <v>2093</v>
+        <v>2092</v>
       </c>
       <c r="G570">
         <v>10</v>
@@ -17580,7 +17577,7 @@
         <v>281386</v>
       </c>
       <c r="C571" t="s">
-        <v>2094</v>
+        <v>2093</v>
       </c>
       <c r="G571">
         <v>10</v>
@@ -17597,7 +17594,7 @@
         <v>281387</v>
       </c>
       <c r="C572" t="s">
-        <v>2029</v>
+        <v>2028</v>
       </c>
       <c r="G572">
         <v>10</v>
@@ -17614,7 +17611,7 @@
         <v>281388</v>
       </c>
       <c r="C573" t="s">
-        <v>2092</v>
+        <v>2091</v>
       </c>
       <c r="G573">
         <v>10</v>
@@ -17631,7 +17628,7 @@
         <v>281438</v>
       </c>
       <c r="C574" t="s">
-        <v>2161</v>
+        <v>2160</v>
       </c>
       <c r="G574">
         <v>10</v>
@@ -17648,7 +17645,7 @@
         <v>281439</v>
       </c>
       <c r="C575" t="s">
-        <v>2162</v>
+        <v>2161</v>
       </c>
       <c r="G575">
         <v>10</v>
@@ -17665,7 +17662,7 @@
         <v>281440</v>
       </c>
       <c r="C576" t="s">
-        <v>2177</v>
+        <v>2176</v>
       </c>
       <c r="G576">
         <v>10</v>
@@ -17682,7 +17679,7 @@
         <v>281443</v>
       </c>
       <c r="C577" t="s">
-        <v>2163</v>
+        <v>2162</v>
       </c>
       <c r="G577">
         <v>10</v>
@@ -17699,7 +17696,7 @@
         <v>281444</v>
       </c>
       <c r="C578" t="s">
-        <v>2178</v>
+        <v>2177</v>
       </c>
       <c r="G578">
         <v>10</v>
@@ -17716,7 +17713,7 @@
         <v>281445</v>
       </c>
       <c r="C579" t="s">
-        <v>2166</v>
+        <v>2165</v>
       </c>
       <c r="G579">
         <v>10</v>
@@ -17733,7 +17730,7 @@
         <v>281446</v>
       </c>
       <c r="C580" t="s">
-        <v>2167</v>
+        <v>2166</v>
       </c>
       <c r="G580">
         <v>10</v>
@@ -17750,7 +17747,7 @@
         <v>281447</v>
       </c>
       <c r="C581" t="s">
-        <v>2168</v>
+        <v>2167</v>
       </c>
       <c r="G581">
         <v>10</v>
@@ -17767,7 +17764,7 @@
         <v>281448</v>
       </c>
       <c r="C582" t="s">
-        <v>2179</v>
+        <v>2178</v>
       </c>
       <c r="G582">
         <v>10</v>
@@ -17784,7 +17781,7 @@
         <v>281449</v>
       </c>
       <c r="C583" t="s">
-        <v>2169</v>
+        <v>2168</v>
       </c>
       <c r="G583">
         <v>10</v>
@@ -17801,7 +17798,7 @@
         <v>281450</v>
       </c>
       <c r="C584" t="s">
-        <v>2180</v>
+        <v>2179</v>
       </c>
       <c r="G584">
         <v>10</v>
@@ -17818,7 +17815,7 @@
         <v>281451</v>
       </c>
       <c r="C585" t="s">
-        <v>2095</v>
+        <v>2094</v>
       </c>
       <c r="G585">
         <v>10</v>
@@ -17835,7 +17832,7 @@
         <v>281452</v>
       </c>
       <c r="C586" t="s">
-        <v>2096</v>
+        <v>2095</v>
       </c>
       <c r="G586">
         <v>10</v>
@@ -17852,7 +17849,7 @@
         <v>281454</v>
       </c>
       <c r="C587" t="s">
-        <v>2170</v>
+        <v>2169</v>
       </c>
       <c r="G587">
         <v>10</v>
@@ -17869,7 +17866,7 @@
         <v>281455</v>
       </c>
       <c r="C588" t="s">
-        <v>2164</v>
+        <v>2163</v>
       </c>
       <c r="G588">
         <v>10</v>
@@ -17886,7 +17883,7 @@
         <v>281456</v>
       </c>
       <c r="C589" t="s">
-        <v>2181</v>
+        <v>2180</v>
       </c>
       <c r="G589">
         <v>10</v>
@@ -17903,7 +17900,7 @@
         <v>281458</v>
       </c>
       <c r="C590" t="s">
-        <v>2097</v>
+        <v>2096</v>
       </c>
       <c r="G590">
         <v>10</v>
@@ -17920,7 +17917,7 @@
         <v>281460</v>
       </c>
       <c r="C591" t="s">
-        <v>2098</v>
+        <v>2097</v>
       </c>
       <c r="G591">
         <v>10</v>
@@ -17937,7 +17934,7 @@
         <v>281461</v>
       </c>
       <c r="C592" t="s">
-        <v>2182</v>
+        <v>2181</v>
       </c>
       <c r="G592">
         <v>10</v>
@@ -17954,7 +17951,7 @@
         <v>281463</v>
       </c>
       <c r="C593" t="s">
-        <v>2183</v>
+        <v>2182</v>
       </c>
       <c r="G593">
         <v>10</v>
@@ -17971,7 +17968,7 @@
         <v>281464</v>
       </c>
       <c r="C594" t="s">
-        <v>2184</v>
+        <v>2183</v>
       </c>
       <c r="G594">
         <v>10</v>
@@ -17988,7 +17985,7 @@
         <v>281465</v>
       </c>
       <c r="C595" t="s">
-        <v>2185</v>
+        <v>2184</v>
       </c>
       <c r="G595">
         <v>10</v>
@@ -18005,7 +18002,7 @@
         <v>281466</v>
       </c>
       <c r="C596" t="s">
-        <v>2171</v>
+        <v>2170</v>
       </c>
       <c r="G596">
         <v>10</v>
@@ -18022,7 +18019,7 @@
         <v>281468</v>
       </c>
       <c r="C597" t="s">
-        <v>2172</v>
+        <v>2171</v>
       </c>
       <c r="G597">
         <v>10</v>
@@ -18039,7 +18036,7 @@
         <v>281469</v>
       </c>
       <c r="C598" t="s">
-        <v>2186</v>
+        <v>2185</v>
       </c>
       <c r="G598">
         <v>10</v>
@@ -18056,7 +18053,7 @@
         <v>281471</v>
       </c>
       <c r="C599" t="s">
-        <v>2099</v>
+        <v>2098</v>
       </c>
       <c r="G599">
         <v>10</v>
@@ -18073,7 +18070,7 @@
         <v>281472</v>
       </c>
       <c r="C600" t="s">
-        <v>2100</v>
+        <v>2099</v>
       </c>
       <c r="G600">
         <v>10</v>
@@ -18090,7 +18087,7 @@
         <v>281473</v>
       </c>
       <c r="C601" t="s">
-        <v>2173</v>
+        <v>2172</v>
       </c>
       <c r="G601">
         <v>10</v>
@@ -18107,7 +18104,7 @@
         <v>281474</v>
       </c>
       <c r="C602" t="s">
-        <v>2174</v>
+        <v>2173</v>
       </c>
       <c r="G602">
         <v>10</v>
@@ -18124,7 +18121,7 @@
         <v>281475</v>
       </c>
       <c r="C603" t="s">
-        <v>2101</v>
+        <v>2100</v>
       </c>
       <c r="G603">
         <v>10</v>
@@ -18141,7 +18138,7 @@
         <v>281476</v>
       </c>
       <c r="C604" t="s">
-        <v>2187</v>
+        <v>2186</v>
       </c>
       <c r="G604">
         <v>10</v>
@@ -18158,7 +18155,7 @@
         <v>281477</v>
       </c>
       <c r="C605" t="s">
-        <v>2102</v>
+        <v>2101</v>
       </c>
       <c r="G605">
         <v>10</v>
@@ -18175,7 +18172,7 @@
         <v>281478</v>
       </c>
       <c r="C606" t="s">
-        <v>2103</v>
+        <v>2102</v>
       </c>
       <c r="G606">
         <v>10</v>
@@ -18192,7 +18189,7 @@
         <v>281479</v>
       </c>
       <c r="C607" t="s">
-        <v>2104</v>
+        <v>2103</v>
       </c>
       <c r="G607">
         <v>10</v>
@@ -18209,7 +18206,7 @@
         <v>281480</v>
       </c>
       <c r="C608" t="s">
-        <v>2188</v>
+        <v>2187</v>
       </c>
       <c r="G608">
         <v>10</v>
@@ -18226,7 +18223,7 @@
         <v>281481</v>
       </c>
       <c r="C609" t="s">
-        <v>2175</v>
+        <v>2174</v>
       </c>
       <c r="G609">
         <v>10</v>
@@ -18243,7 +18240,7 @@
         <v>281482</v>
       </c>
       <c r="C610" t="s">
-        <v>2105</v>
+        <v>2104</v>
       </c>
       <c r="G610">
         <v>10</v>
@@ -18260,7 +18257,7 @@
         <v>281483</v>
       </c>
       <c r="C611" t="s">
-        <v>2176</v>
+        <v>2175</v>
       </c>
       <c r="G611">
         <v>10</v>
@@ -18277,7 +18274,7 @@
         <v>281484</v>
       </c>
       <c r="C612" t="s">
-        <v>2106</v>
+        <v>2105</v>
       </c>
       <c r="G612">
         <v>10</v>
@@ -18294,7 +18291,7 @@
         <v>281485</v>
       </c>
       <c r="C613" t="s">
-        <v>2165</v>
+        <v>2164</v>
       </c>
       <c r="G613">
         <v>10</v>
@@ -18311,7 +18308,7 @@
         <v>281486</v>
       </c>
       <c r="C614" t="s">
-        <v>2189</v>
+        <v>2188</v>
       </c>
       <c r="G614">
         <v>10</v>
@@ -18328,7 +18325,7 @@
         <v>281487</v>
       </c>
       <c r="C615" t="s">
-        <v>2107</v>
+        <v>2106</v>
       </c>
       <c r="G615">
         <v>10</v>
@@ -18345,7 +18342,7 @@
         <v>281488</v>
       </c>
       <c r="C616" t="s">
-        <v>2108</v>
+        <v>2107</v>
       </c>
       <c r="G616">
         <v>10</v>
@@ -18362,7 +18359,7 @@
         <v>281489</v>
       </c>
       <c r="C617" t="s">
-        <v>2109</v>
+        <v>2108</v>
       </c>
       <c r="G617">
         <v>10</v>
@@ -18379,7 +18376,7 @@
         <v>281490</v>
       </c>
       <c r="C618" t="s">
-        <v>2110</v>
+        <v>2109</v>
       </c>
       <c r="G618">
         <v>10</v>
@@ -18396,7 +18393,7 @@
         <v>281491</v>
       </c>
       <c r="C619" t="s">
-        <v>2190</v>
+        <v>2189</v>
       </c>
       <c r="G619">
         <v>10</v>
@@ -18413,7 +18410,7 @@
         <v>281492</v>
       </c>
       <c r="C620" t="s">
-        <v>2191</v>
+        <v>2190</v>
       </c>
       <c r="G620">
         <v>10</v>
@@ -18430,7 +18427,7 @@
         <v>281542</v>
       </c>
       <c r="C621" t="s">
-        <v>2200</v>
+        <v>2199</v>
       </c>
       <c r="G621">
         <v>11</v>
@@ -18447,7 +18444,7 @@
         <v>281543</v>
       </c>
       <c r="C622" t="s">
-        <v>2193</v>
+        <v>2192</v>
       </c>
       <c r="G622">
         <v>11</v>
@@ -18481,7 +18478,7 @@
         <v>281545</v>
       </c>
       <c r="C624" t="s">
-        <v>2194</v>
+        <v>2193</v>
       </c>
       <c r="G624">
         <v>11</v>
@@ -18498,7 +18495,7 @@
         <v>281546</v>
       </c>
       <c r="C625" t="s">
-        <v>2195</v>
+        <v>2194</v>
       </c>
       <c r="G625">
         <v>11</v>
@@ -18549,7 +18546,7 @@
         <v>281549</v>
       </c>
       <c r="C628" t="s">
-        <v>2196</v>
+        <v>2195</v>
       </c>
       <c r="G628">
         <v>11</v>
@@ -18566,7 +18563,7 @@
         <v>281550</v>
       </c>
       <c r="C629" t="s">
-        <v>2197</v>
+        <v>2196</v>
       </c>
       <c r="G629">
         <v>11</v>
@@ -18583,7 +18580,7 @@
         <v>281551</v>
       </c>
       <c r="C630" t="s">
-        <v>2198</v>
+        <v>2197</v>
       </c>
       <c r="G630">
         <v>11</v>
@@ -18600,7 +18597,7 @@
         <v>281552</v>
       </c>
       <c r="C631" t="s">
-        <v>2199</v>
+        <v>2198</v>
       </c>
       <c r="G631">
         <v>11</v>
@@ -18617,7 +18614,7 @@
         <v>281553</v>
       </c>
       <c r="C632" t="s">
-        <v>2201</v>
+        <v>2200</v>
       </c>
       <c r="G632">
         <v>11</v>
@@ -18651,7 +18648,7 @@
         <v>281604</v>
       </c>
       <c r="C634" t="s">
-        <v>2202</v>
+        <v>2201</v>
       </c>
       <c r="G634">
         <v>11</v>
@@ -18668,7 +18665,7 @@
         <v>281606</v>
       </c>
       <c r="C635" t="s">
-        <v>2203</v>
+        <v>2202</v>
       </c>
       <c r="G635">
         <v>11</v>
@@ -18685,7 +18682,7 @@
         <v>281607</v>
       </c>
       <c r="C636" t="s">
-        <v>2204</v>
+        <v>2203</v>
       </c>
       <c r="G636">
         <v>11</v>
@@ -18702,7 +18699,7 @@
         <v>281608</v>
       </c>
       <c r="C637" t="s">
-        <v>2205</v>
+        <v>2204</v>
       </c>
       <c r="G637">
         <v>11</v>
@@ -18719,7 +18716,7 @@
         <v>281609</v>
       </c>
       <c r="C638" t="s">
-        <v>2206</v>
+        <v>2205</v>
       </c>
       <c r="G638">
         <v>11</v>
@@ -18736,7 +18733,7 @@
         <v>281610</v>
       </c>
       <c r="C639" t="s">
-        <v>2207</v>
+        <v>2206</v>
       </c>
       <c r="G639">
         <v>11</v>
@@ -18753,7 +18750,7 @@
         <v>281611</v>
       </c>
       <c r="C640" t="s">
-        <v>2208</v>
+        <v>2207</v>
       </c>
       <c r="G640">
         <v>11</v>
@@ -18770,7 +18767,7 @@
         <v>281613</v>
       </c>
       <c r="C641" t="s">
-        <v>2209</v>
+        <v>2208</v>
       </c>
       <c r="G641">
         <v>11</v>
@@ -18787,7 +18784,7 @@
         <v>281614</v>
       </c>
       <c r="C642" t="s">
-        <v>2561</v>
+        <v>2560</v>
       </c>
       <c r="G642">
         <v>11</v>
@@ -18804,7 +18801,7 @@
         <v>281616</v>
       </c>
       <c r="C643" t="s">
-        <v>2210</v>
+        <v>2209</v>
       </c>
       <c r="G643">
         <v>11</v>
@@ -18821,7 +18818,7 @@
         <v>281617</v>
       </c>
       <c r="C644" t="s">
-        <v>2211</v>
+        <v>2210</v>
       </c>
       <c r="G644">
         <v>11</v>
@@ -18838,7 +18835,7 @@
         <v>281618</v>
       </c>
       <c r="C645" t="s">
-        <v>2331</v>
+        <v>2330</v>
       </c>
       <c r="G645">
         <v>11</v>
@@ -18855,7 +18852,7 @@
         <v>281619</v>
       </c>
       <c r="C646" t="s">
-        <v>2212</v>
+        <v>2211</v>
       </c>
       <c r="G646">
         <v>11</v>
@@ -18872,7 +18869,7 @@
         <v>281620</v>
       </c>
       <c r="C647" t="s">
-        <v>2213</v>
+        <v>2212</v>
       </c>
       <c r="G647">
         <v>11</v>
@@ -18889,7 +18886,7 @@
         <v>281622</v>
       </c>
       <c r="C648" t="s">
-        <v>2214</v>
+        <v>2213</v>
       </c>
       <c r="G648">
         <v>11</v>
@@ -18906,7 +18903,7 @@
         <v>281624</v>
       </c>
       <c r="C649" t="s">
-        <v>2215</v>
+        <v>2214</v>
       </c>
       <c r="G649">
         <v>11</v>
@@ -18923,7 +18920,7 @@
         <v>281626</v>
       </c>
       <c r="C650" t="s">
-        <v>2216</v>
+        <v>2215</v>
       </c>
       <c r="G650">
         <v>11</v>
@@ -18940,7 +18937,7 @@
         <v>281628</v>
       </c>
       <c r="C651" t="s">
-        <v>2217</v>
+        <v>2216</v>
       </c>
       <c r="G651">
         <v>11</v>
@@ -18957,7 +18954,7 @@
         <v>281629</v>
       </c>
       <c r="C652" t="s">
-        <v>2218</v>
+        <v>2217</v>
       </c>
       <c r="G652">
         <v>11</v>
@@ -18974,7 +18971,7 @@
         <v>281631</v>
       </c>
       <c r="C653" t="s">
-        <v>2219</v>
+        <v>2218</v>
       </c>
       <c r="G653">
         <v>11</v>
@@ -18991,7 +18988,7 @@
         <v>281636</v>
       </c>
       <c r="C654" t="s">
-        <v>2220</v>
+        <v>2219</v>
       </c>
       <c r="G654">
         <v>11</v>
@@ -19008,7 +19005,7 @@
         <v>281637</v>
       </c>
       <c r="C655" t="s">
-        <v>2221</v>
+        <v>2220</v>
       </c>
       <c r="G655">
         <v>11</v>
@@ -19025,7 +19022,7 @@
         <v>281638</v>
       </c>
       <c r="C656" t="s">
-        <v>2222</v>
+        <v>2221</v>
       </c>
       <c r="G656">
         <v>11</v>
@@ -19042,7 +19039,7 @@
         <v>281639</v>
       </c>
       <c r="C657" t="s">
-        <v>2223</v>
+        <v>2222</v>
       </c>
       <c r="G657">
         <v>11</v>
@@ -19059,7 +19056,7 @@
         <v>281641</v>
       </c>
       <c r="C658" t="s">
-        <v>2224</v>
+        <v>2223</v>
       </c>
       <c r="G658">
         <v>11</v>
@@ -19076,7 +19073,7 @@
         <v>281642</v>
       </c>
       <c r="C659" t="s">
-        <v>2332</v>
+        <v>2331</v>
       </c>
       <c r="G659">
         <v>11</v>
@@ -19093,7 +19090,7 @@
         <v>281644</v>
       </c>
       <c r="C660" t="s">
-        <v>2333</v>
+        <v>2332</v>
       </c>
       <c r="G660">
         <v>11</v>
@@ -19110,7 +19107,7 @@
         <v>281645</v>
       </c>
       <c r="C661" t="s">
-        <v>2225</v>
+        <v>2224</v>
       </c>
       <c r="G661">
         <v>11</v>
@@ -19127,7 +19124,7 @@
         <v>281646</v>
       </c>
       <c r="C662" t="s">
-        <v>2334</v>
+        <v>2333</v>
       </c>
       <c r="G662">
         <v>11</v>
@@ -19144,7 +19141,7 @@
         <v>281650</v>
       </c>
       <c r="C663" t="s">
-        <v>2226</v>
+        <v>2225</v>
       </c>
       <c r="G663">
         <v>11</v>
@@ -19161,7 +19158,7 @@
         <v>281654</v>
       </c>
       <c r="C664" t="s">
-        <v>2335</v>
+        <v>2334</v>
       </c>
       <c r="G664">
         <v>11</v>
@@ -19178,7 +19175,7 @@
         <v>281656</v>
       </c>
       <c r="C665" t="s">
-        <v>2227</v>
+        <v>2226</v>
       </c>
       <c r="G665">
         <v>11</v>
@@ -19195,7 +19192,7 @@
         <v>281662</v>
       </c>
       <c r="C666" t="s">
-        <v>2336</v>
+        <v>2335</v>
       </c>
       <c r="G666">
         <v>11</v>
@@ -19212,7 +19209,7 @@
         <v>281666</v>
       </c>
       <c r="C667" t="s">
-        <v>2337</v>
+        <v>2336</v>
       </c>
       <c r="G667">
         <v>11</v>
@@ -19229,7 +19226,7 @@
         <v>281669</v>
       </c>
       <c r="C668" t="s">
-        <v>2228</v>
+        <v>2227</v>
       </c>
       <c r="G668">
         <v>11</v>
@@ -19246,7 +19243,7 @@
         <v>281670</v>
       </c>
       <c r="C669" t="s">
-        <v>2338</v>
+        <v>2337</v>
       </c>
       <c r="G669">
         <v>11</v>
@@ -19263,7 +19260,7 @@
         <v>281671</v>
       </c>
       <c r="C670" t="s">
-        <v>2339</v>
+        <v>2338</v>
       </c>
       <c r="G670">
         <v>11</v>
@@ -19280,7 +19277,7 @@
         <v>281672</v>
       </c>
       <c r="C671" t="s">
-        <v>2229</v>
+        <v>2228</v>
       </c>
       <c r="G671">
         <v>11</v>
@@ -19297,7 +19294,7 @@
         <v>281674</v>
       </c>
       <c r="C672" t="s">
-        <v>2340</v>
+        <v>2339</v>
       </c>
       <c r="G672">
         <v>11</v>
@@ -19314,7 +19311,7 @@
         <v>281675</v>
       </c>
       <c r="C673" t="s">
-        <v>2230</v>
+        <v>2229</v>
       </c>
       <c r="G673">
         <v>11</v>
@@ -19331,7 +19328,7 @@
         <v>281677</v>
       </c>
       <c r="C674" t="s">
-        <v>2231</v>
+        <v>2230</v>
       </c>
       <c r="G674">
         <v>11</v>
@@ -19348,7 +19345,7 @@
         <v>281679</v>
       </c>
       <c r="C675" t="s">
-        <v>2232</v>
+        <v>2231</v>
       </c>
       <c r="G675">
         <v>11</v>
@@ -19365,7 +19362,7 @@
         <v>281681</v>
       </c>
       <c r="C676" t="s">
-        <v>2233</v>
+        <v>2232</v>
       </c>
       <c r="G676">
         <v>11</v>
@@ -19382,7 +19379,7 @@
         <v>281683</v>
       </c>
       <c r="C677" t="s">
-        <v>2341</v>
+        <v>2340</v>
       </c>
       <c r="G677">
         <v>11</v>
@@ -19399,7 +19396,7 @@
         <v>281684</v>
       </c>
       <c r="C678" t="s">
-        <v>2342</v>
+        <v>2341</v>
       </c>
       <c r="G678">
         <v>11</v>
@@ -19416,7 +19413,7 @@
         <v>281686</v>
       </c>
       <c r="C679" t="s">
-        <v>2234</v>
+        <v>2233</v>
       </c>
       <c r="G679">
         <v>11</v>
@@ -19433,7 +19430,7 @@
         <v>281687</v>
       </c>
       <c r="C680" t="s">
-        <v>2235</v>
+        <v>2234</v>
       </c>
       <c r="G680">
         <v>11</v>
@@ -19450,7 +19447,7 @@
         <v>281688</v>
       </c>
       <c r="C681" t="s">
-        <v>2236</v>
+        <v>2235</v>
       </c>
       <c r="G681">
         <v>11</v>
@@ -19467,7 +19464,7 @@
         <v>281689</v>
       </c>
       <c r="C682" t="s">
-        <v>2237</v>
+        <v>2236</v>
       </c>
       <c r="G682">
         <v>11</v>
@@ -19484,7 +19481,7 @@
         <v>281692</v>
       </c>
       <c r="C683" t="s">
-        <v>2343</v>
+        <v>2342</v>
       </c>
       <c r="G683">
         <v>11</v>
@@ -19501,7 +19498,7 @@
         <v>281693</v>
       </c>
       <c r="C684" t="s">
-        <v>2344</v>
+        <v>2343</v>
       </c>
       <c r="G684">
         <v>11</v>
@@ -19518,7 +19515,7 @@
         <v>281694</v>
       </c>
       <c r="C685" t="s">
-        <v>2238</v>
+        <v>2237</v>
       </c>
       <c r="G685">
         <v>11</v>
@@ -19535,7 +19532,7 @@
         <v>281695</v>
       </c>
       <c r="C686" t="s">
-        <v>2345</v>
+        <v>2344</v>
       </c>
       <c r="G686">
         <v>11</v>
@@ -19552,7 +19549,7 @@
         <v>281696</v>
       </c>
       <c r="C687" t="s">
-        <v>2239</v>
+        <v>2238</v>
       </c>
       <c r="G687">
         <v>11</v>
@@ -19569,7 +19566,7 @@
         <v>281697</v>
       </c>
       <c r="C688" t="s">
-        <v>2346</v>
+        <v>2345</v>
       </c>
       <c r="G688">
         <v>11</v>
@@ -19586,7 +19583,7 @@
         <v>281699</v>
       </c>
       <c r="C689" t="s">
-        <v>2347</v>
+        <v>2346</v>
       </c>
       <c r="G689">
         <v>11</v>
@@ -19603,7 +19600,7 @@
         <v>281700</v>
       </c>
       <c r="C690" t="s">
-        <v>2348</v>
+        <v>2347</v>
       </c>
       <c r="G690">
         <v>11</v>
@@ -19620,7 +19617,7 @@
         <v>281702</v>
       </c>
       <c r="C691" t="s">
-        <v>2349</v>
+        <v>2348</v>
       </c>
       <c r="G691">
         <v>11</v>
@@ -19637,7 +19634,7 @@
         <v>281752</v>
       </c>
       <c r="C692" t="s">
-        <v>2199</v>
+        <v>2198</v>
       </c>
       <c r="G692">
         <v>12</v>
@@ -19654,7 +19651,7 @@
         <v>281753</v>
       </c>
       <c r="C693" t="s">
-        <v>2350</v>
+        <v>2349</v>
       </c>
       <c r="G693">
         <v>12</v>
@@ -19671,7 +19668,7 @@
         <v>281754</v>
       </c>
       <c r="C694" t="s">
-        <v>2351</v>
+        <v>2350</v>
       </c>
       <c r="G694">
         <v>12</v>
@@ -19705,7 +19702,7 @@
         <v>281808</v>
       </c>
       <c r="C696" t="s">
-        <v>2352</v>
+        <v>2351</v>
       </c>
       <c r="G696">
         <v>12</v>
@@ -19722,7 +19719,7 @@
         <v>281809</v>
       </c>
       <c r="C697" t="s">
-        <v>2451</v>
+        <v>2450</v>
       </c>
       <c r="G697">
         <v>12</v>
@@ -19739,7 +19736,7 @@
         <v>281810</v>
       </c>
       <c r="C698" t="s">
-        <v>2452</v>
+        <v>2451</v>
       </c>
       <c r="G698">
         <v>12</v>
@@ -19756,7 +19753,7 @@
         <v>281814</v>
       </c>
       <c r="C699" t="s">
-        <v>2453</v>
+        <v>2452</v>
       </c>
       <c r="G699">
         <v>12</v>
@@ -19773,7 +19770,7 @@
         <v>281815</v>
       </c>
       <c r="C700" t="s">
-        <v>2454</v>
+        <v>2453</v>
       </c>
       <c r="G700">
         <v>12</v>
@@ -19790,7 +19787,7 @@
         <v>281818</v>
       </c>
       <c r="C701" t="s">
-        <v>2455</v>
+        <v>2454</v>
       </c>
       <c r="G701">
         <v>12</v>
@@ -19807,7 +19804,7 @@
         <v>281819</v>
       </c>
       <c r="C702" t="s">
-        <v>2456</v>
+        <v>2455</v>
       </c>
       <c r="G702">
         <v>12</v>
@@ -19824,7 +19821,7 @@
         <v>281820</v>
       </c>
       <c r="C703" t="s">
-        <v>2457</v>
+        <v>2456</v>
       </c>
       <c r="G703">
         <v>12</v>
@@ -19841,7 +19838,7 @@
         <v>281821</v>
       </c>
       <c r="C704" t="s">
-        <v>2458</v>
+        <v>2457</v>
       </c>
       <c r="G704">
         <v>12</v>
@@ -19858,7 +19855,7 @@
         <v>281822</v>
       </c>
       <c r="C705" t="s">
-        <v>2459</v>
+        <v>2458</v>
       </c>
       <c r="G705">
         <v>12</v>
@@ -19875,7 +19872,7 @@
         <v>281823</v>
       </c>
       <c r="C706" t="s">
-        <v>2460</v>
+        <v>2459</v>
       </c>
       <c r="G706">
         <v>12</v>
@@ -19892,7 +19889,7 @@
         <v>281824</v>
       </c>
       <c r="C707" t="s">
-        <v>2353</v>
+        <v>2352</v>
       </c>
       <c r="G707">
         <v>12</v>
@@ -19909,7 +19906,7 @@
         <v>281825</v>
       </c>
       <c r="C708" t="s">
-        <v>2354</v>
+        <v>2353</v>
       </c>
       <c r="G708">
         <v>12</v>
@@ -19926,7 +19923,7 @@
         <v>281827</v>
       </c>
       <c r="C709" t="s">
-        <v>2461</v>
+        <v>2460</v>
       </c>
       <c r="G709">
         <v>12</v>
@@ -19943,7 +19940,7 @@
         <v>281828</v>
       </c>
       <c r="C710" t="s">
-        <v>2355</v>
+        <v>2354</v>
       </c>
       <c r="G710">
         <v>12</v>
@@ -19960,7 +19957,7 @@
         <v>281829</v>
       </c>
       <c r="C711" t="s">
-        <v>2356</v>
+        <v>2355</v>
       </c>
       <c r="G711">
         <v>12</v>
@@ -19977,7 +19974,7 @@
         <v>281830</v>
       </c>
       <c r="C712" t="s">
-        <v>2462</v>
+        <v>2461</v>
       </c>
       <c r="G712">
         <v>12</v>
@@ -19994,7 +19991,7 @@
         <v>281831</v>
       </c>
       <c r="C713" t="s">
-        <v>2463</v>
+        <v>2462</v>
       </c>
       <c r="G713">
         <v>12</v>
@@ -20011,7 +20008,7 @@
         <v>281832</v>
       </c>
       <c r="C714" t="s">
-        <v>2464</v>
+        <v>2463</v>
       </c>
       <c r="G714">
         <v>12</v>
@@ -20028,7 +20025,7 @@
         <v>281833</v>
       </c>
       <c r="C715" t="s">
-        <v>2465</v>
+        <v>2464</v>
       </c>
       <c r="G715">
         <v>12</v>
@@ -20045,7 +20042,7 @@
         <v>281834</v>
       </c>
       <c r="C716" t="s">
-        <v>2357</v>
+        <v>2356</v>
       </c>
       <c r="G716">
         <v>12</v>
@@ -20062,7 +20059,7 @@
         <v>281835</v>
       </c>
       <c r="C717" t="s">
-        <v>2358</v>
+        <v>2357</v>
       </c>
       <c r="G717">
         <v>12</v>
@@ -20079,7 +20076,7 @@
         <v>281836</v>
       </c>
       <c r="C718" t="s">
-        <v>2359</v>
+        <v>2358</v>
       </c>
       <c r="G718">
         <v>12</v>
@@ -20096,7 +20093,7 @@
         <v>281838</v>
       </c>
       <c r="C719" t="s">
-        <v>2466</v>
+        <v>2465</v>
       </c>
       <c r="G719">
         <v>12</v>
@@ -20113,7 +20110,7 @@
         <v>281840</v>
       </c>
       <c r="C720" t="s">
-        <v>2467</v>
+        <v>2466</v>
       </c>
       <c r="G720">
         <v>12</v>
@@ -20130,7 +20127,7 @@
         <v>281841</v>
       </c>
       <c r="C721" t="s">
-        <v>2468</v>
+        <v>2467</v>
       </c>
       <c r="G721">
         <v>12</v>
@@ -20147,7 +20144,7 @@
         <v>281842</v>
       </c>
       <c r="C722" t="s">
-        <v>2360</v>
+        <v>2359</v>
       </c>
       <c r="G722">
         <v>12</v>
@@ -20164,7 +20161,7 @@
         <v>281843</v>
       </c>
       <c r="C723" t="s">
-        <v>2469</v>
+        <v>2468</v>
       </c>
       <c r="G723">
         <v>12</v>
@@ -20181,7 +20178,7 @@
         <v>281844</v>
       </c>
       <c r="C724" t="s">
-        <v>2361</v>
+        <v>2360</v>
       </c>
       <c r="G724">
         <v>12</v>
@@ -20198,7 +20195,7 @@
         <v>281845</v>
       </c>
       <c r="C725" t="s">
-        <v>2362</v>
+        <v>2361</v>
       </c>
       <c r="G725">
         <v>12</v>
@@ -20215,7 +20212,7 @@
         <v>281846</v>
       </c>
       <c r="C726" t="s">
-        <v>2470</v>
+        <v>2469</v>
       </c>
       <c r="G726">
         <v>12</v>
@@ -20232,7 +20229,7 @@
         <v>281847</v>
       </c>
       <c r="C727" t="s">
-        <v>2471</v>
+        <v>2470</v>
       </c>
       <c r="G727">
         <v>12</v>
@@ -20249,7 +20246,7 @@
         <v>281848</v>
       </c>
       <c r="C728" t="s">
-        <v>2363</v>
+        <v>2362</v>
       </c>
       <c r="G728">
         <v>12</v>
@@ -20266,7 +20263,7 @@
         <v>281849</v>
       </c>
       <c r="C729" t="s">
-        <v>2364</v>
+        <v>2363</v>
       </c>
       <c r="G729">
         <v>12</v>
@@ -20283,7 +20280,7 @@
         <v>281850</v>
       </c>
       <c r="C730" t="s">
-        <v>2365</v>
+        <v>2364</v>
       </c>
       <c r="G730">
         <v>12</v>
@@ -20300,7 +20297,7 @@
         <v>281851</v>
       </c>
       <c r="C731" t="s">
-        <v>2366</v>
+        <v>2365</v>
       </c>
       <c r="G731">
         <v>12</v>
@@ -20317,7 +20314,7 @@
         <v>281852</v>
       </c>
       <c r="C732" t="s">
-        <v>2367</v>
+        <v>2366</v>
       </c>
       <c r="G732">
         <v>12</v>
@@ -20334,7 +20331,7 @@
         <v>281853</v>
       </c>
       <c r="C733" t="s">
-        <v>2472</v>
+        <v>2471</v>
       </c>
       <c r="G733">
         <v>12</v>
@@ -20351,7 +20348,7 @@
         <v>281854</v>
       </c>
       <c r="C734" t="s">
-        <v>2368</v>
+        <v>2367</v>
       </c>
       <c r="G734">
         <v>12</v>
@@ -20368,7 +20365,7 @@
         <v>281855</v>
       </c>
       <c r="C735" t="s">
-        <v>2369</v>
+        <v>2368</v>
       </c>
       <c r="G735">
         <v>12</v>
@@ -20385,7 +20382,7 @@
         <v>281857</v>
       </c>
       <c r="C736" t="s">
-        <v>2370</v>
+        <v>2369</v>
       </c>
       <c r="G736">
         <v>12</v>
@@ -20402,7 +20399,7 @@
         <v>281859</v>
       </c>
       <c r="C737" t="s">
-        <v>2371</v>
+        <v>2370</v>
       </c>
       <c r="G737">
         <v>12</v>
@@ -20419,7 +20416,7 @@
         <v>281861</v>
       </c>
       <c r="C738" t="s">
-        <v>2372</v>
+        <v>2371</v>
       </c>
       <c r="G738">
         <v>12</v>
@@ -20436,7 +20433,7 @@
         <v>281862</v>
       </c>
       <c r="C739" t="s">
-        <v>2473</v>
+        <v>2472</v>
       </c>
       <c r="G739">
         <v>12</v>
@@ -20453,7 +20450,7 @@
         <v>281863</v>
       </c>
       <c r="C740" t="s">
-        <v>2474</v>
+        <v>2473</v>
       </c>
       <c r="G740">
         <v>12</v>
@@ -20470,7 +20467,7 @@
         <v>281866</v>
       </c>
       <c r="C741" t="s">
-        <v>2373</v>
+        <v>2372</v>
       </c>
       <c r="G741">
         <v>12</v>
@@ -20487,7 +20484,7 @@
         <v>281867</v>
       </c>
       <c r="C742" t="s">
-        <v>2374</v>
+        <v>2373</v>
       </c>
       <c r="G742">
         <v>12</v>
@@ -20504,7 +20501,7 @@
         <v>281868</v>
       </c>
       <c r="C743" t="s">
-        <v>2475</v>
+        <v>2474</v>
       </c>
       <c r="G743">
         <v>12</v>
@@ -20521,7 +20518,7 @@
         <v>281869</v>
       </c>
       <c r="C744" t="s">
-        <v>2476</v>
+        <v>2475</v>
       </c>
       <c r="G744">
         <v>12</v>
@@ -20538,7 +20535,7 @@
         <v>281870</v>
       </c>
       <c r="C745" t="s">
-        <v>2375</v>
+        <v>2374</v>
       </c>
       <c r="G745">
         <v>12</v>
@@ -20555,7 +20552,7 @@
         <v>281871</v>
       </c>
       <c r="C746" t="s">
-        <v>2376</v>
+        <v>2375</v>
       </c>
       <c r="G746">
         <v>12</v>
@@ -20572,7 +20569,7 @@
         <v>281872</v>
       </c>
       <c r="C747" t="s">
-        <v>2477</v>
+        <v>2476</v>
       </c>
       <c r="G747">
         <v>12</v>
@@ -20589,7 +20586,7 @@
         <v>281873</v>
       </c>
       <c r="C748" t="s">
-        <v>2377</v>
+        <v>2376</v>
       </c>
       <c r="G748">
         <v>12</v>
@@ -20606,7 +20603,7 @@
         <v>281874</v>
       </c>
       <c r="C749" t="s">
-        <v>2450</v>
+        <v>2449</v>
       </c>
       <c r="G749">
         <v>12</v>
@@ -20623,7 +20620,7 @@
         <v>281875</v>
       </c>
       <c r="C750" t="s">
-        <v>2378</v>
+        <v>2377</v>
       </c>
       <c r="G750">
         <v>12</v>
@@ -20640,7 +20637,7 @@
         <v>281876</v>
       </c>
       <c r="C751" t="s">
-        <v>2379</v>
+        <v>2378</v>
       </c>
       <c r="G751">
         <v>12</v>
@@ -20657,7 +20654,7 @@
         <v>281877</v>
       </c>
       <c r="C752" t="s">
-        <v>2380</v>
+        <v>2379</v>
       </c>
       <c r="G752">
         <v>12</v>
@@ -20674,7 +20671,7 @@
         <v>281878</v>
       </c>
       <c r="C753" t="s">
-        <v>2478</v>
+        <v>2477</v>
       </c>
       <c r="G753">
         <v>12</v>
@@ -20691,7 +20688,7 @@
         <v>281879</v>
       </c>
       <c r="C754" t="s">
-        <v>2381</v>
+        <v>2380</v>
       </c>
       <c r="G754">
         <v>12</v>
@@ -20708,7 +20705,7 @@
         <v>281880</v>
       </c>
       <c r="C755" t="s">
-        <v>2382</v>
+        <v>2381</v>
       </c>
       <c r="G755">
         <v>12</v>
@@ -27945,7 +27942,7 @@
         <v>514</v>
       </c>
       <c r="C1270" t="s">
-        <v>2048</v>
+        <v>2047</v>
       </c>
       <c r="I1270" s="47">
         <v>281249</v>
@@ -27959,7 +27956,7 @@
         <v>515</v>
       </c>
       <c r="C1271" t="s">
-        <v>2052</v>
+        <v>2051</v>
       </c>
       <c r="I1271" s="47">
         <v>281299</v>
@@ -27973,7 +27970,7 @@
         <v>516</v>
       </c>
       <c r="C1272" t="s">
-        <v>2053</v>
+        <v>2052</v>
       </c>
       <c r="I1272" s="47">
         <v>281300</v>
@@ -27987,7 +27984,7 @@
         <v>517</v>
       </c>
       <c r="C1273" t="s">
-        <v>2054</v>
+        <v>2053</v>
       </c>
       <c r="I1273" s="47">
         <v>281301</v>
@@ -28001,7 +27998,7 @@
         <v>518</v>
       </c>
       <c r="C1274" t="s">
-        <v>2055</v>
+        <v>2054</v>
       </c>
       <c r="I1274" s="47">
         <v>281302</v>
@@ -28015,7 +28012,7 @@
         <v>519</v>
       </c>
       <c r="C1275" t="s">
-        <v>2056</v>
+        <v>2055</v>
       </c>
       <c r="I1275" s="47">
         <v>281302</v>
@@ -28029,7 +28026,7 @@
         <v>520</v>
       </c>
       <c r="C1276" t="s">
-        <v>2057</v>
+        <v>2056</v>
       </c>
       <c r="I1276" s="47">
         <v>281302</v>
@@ -28043,7 +28040,7 @@
         <v>521</v>
       </c>
       <c r="C1277" t="s">
-        <v>2058</v>
+        <v>2057</v>
       </c>
       <c r="I1277" s="47">
         <v>281302</v>
@@ -28057,7 +28054,7 @@
         <v>522</v>
       </c>
       <c r="C1278" t="s">
-        <v>2059</v>
+        <v>2058</v>
       </c>
       <c r="I1278" s="47">
         <v>281302</v>
@@ -28071,7 +28068,7 @@
         <v>523</v>
       </c>
       <c r="C1279" t="s">
-        <v>2060</v>
+        <v>2059</v>
       </c>
       <c r="I1279" s="47">
         <v>281302</v>
@@ -28085,7 +28082,7 @@
         <v>524</v>
       </c>
       <c r="C1280" t="s">
-        <v>2061</v>
+        <v>2060</v>
       </c>
       <c r="I1280" s="47">
         <v>281302</v>
@@ -28099,7 +28096,7 @@
         <v>525</v>
       </c>
       <c r="C1281" t="s">
-        <v>2062</v>
+        <v>2061</v>
       </c>
       <c r="I1281" s="47">
         <v>281309</v>
@@ -28113,7 +28110,7 @@
         <v>526</v>
       </c>
       <c r="C1282" t="s">
-        <v>2063</v>
+        <v>2062</v>
       </c>
       <c r="I1282" s="47">
         <v>281309</v>
@@ -28127,7 +28124,7 @@
         <v>527</v>
       </c>
       <c r="C1283" t="s">
-        <v>2064</v>
+        <v>2063</v>
       </c>
       <c r="I1283" s="47">
         <v>281311</v>
@@ -28141,7 +28138,7 @@
         <v>528</v>
       </c>
       <c r="C1284" t="s">
-        <v>2065</v>
+        <v>2064</v>
       </c>
       <c r="I1284" s="47">
         <v>281311</v>
@@ -28155,7 +28152,7 @@
         <v>529</v>
       </c>
       <c r="C1285" t="s">
-        <v>2066</v>
+        <v>2065</v>
       </c>
       <c r="I1285" s="47">
         <v>281313</v>
@@ -28169,7 +28166,7 @@
         <v>530</v>
       </c>
       <c r="C1286" t="s">
-        <v>2067</v>
+        <v>2066</v>
       </c>
       <c r="I1286" s="47">
         <v>281314</v>
@@ -28183,7 +28180,7 @@
         <v>531</v>
       </c>
       <c r="C1287" t="s">
-        <v>2068</v>
+        <v>2067</v>
       </c>
       <c r="I1287" s="47">
         <v>281315</v>
@@ -28211,7 +28208,7 @@
         <v>533</v>
       </c>
       <c r="C1289" t="s">
-        <v>2069</v>
+        <v>2068</v>
       </c>
       <c r="I1289" s="47">
         <v>281316</v>
@@ -28225,7 +28222,7 @@
         <v>534</v>
       </c>
       <c r="C1290" t="s">
-        <v>2070</v>
+        <v>2069</v>
       </c>
       <c r="I1290" s="47">
         <v>281316</v>
@@ -28239,7 +28236,7 @@
         <v>535</v>
       </c>
       <c r="C1291" t="s">
-        <v>2071</v>
+        <v>2070</v>
       </c>
       <c r="I1291" s="47">
         <v>281316</v>
@@ -28253,7 +28250,7 @@
         <v>536</v>
       </c>
       <c r="C1292" t="s">
-        <v>2072</v>
+        <v>2071</v>
       </c>
       <c r="I1292" s="47">
         <v>281316</v>
@@ -28281,7 +28278,7 @@
         <v>538</v>
       </c>
       <c r="C1294" t="s">
-        <v>2073</v>
+        <v>2072</v>
       </c>
       <c r="I1294" s="47">
         <v>281322</v>
@@ -28295,7 +28292,7 @@
         <v>539</v>
       </c>
       <c r="C1295" t="s">
-        <v>2074</v>
+        <v>2073</v>
       </c>
       <c r="I1295" s="47">
         <v>281323</v>
@@ -28309,7 +28306,7 @@
         <v>540</v>
       </c>
       <c r="C1296" t="s">
-        <v>2075</v>
+        <v>2074</v>
       </c>
       <c r="I1296" s="47">
         <v>281324</v>
@@ -28337,7 +28334,7 @@
         <v>542</v>
       </c>
       <c r="C1298" t="s">
-        <v>2076</v>
+        <v>2075</v>
       </c>
       <c r="I1298" s="47">
         <v>281326</v>
@@ -28533,7 +28530,7 @@
         <v>556</v>
       </c>
       <c r="C1312" t="s">
-        <v>2111</v>
+        <v>2110</v>
       </c>
       <c r="I1312" s="47">
         <v>281438</v>
@@ -28547,7 +28544,7 @@
         <v>557</v>
       </c>
       <c r="C1313" t="s">
-        <v>2112</v>
+        <v>2111</v>
       </c>
       <c r="I1313" s="47">
         <v>281439</v>
@@ -28561,7 +28558,7 @@
         <v>558</v>
       </c>
       <c r="C1314" t="s">
-        <v>2113</v>
+        <v>2112</v>
       </c>
       <c r="I1314" s="47">
         <v>281440</v>
@@ -28575,7 +28572,7 @@
         <v>559</v>
       </c>
       <c r="C1315" t="s">
-        <v>2114</v>
+        <v>2113</v>
       </c>
       <c r="I1315" s="47">
         <v>281440</v>
@@ -28589,7 +28586,7 @@
         <v>560</v>
       </c>
       <c r="C1316" t="s">
-        <v>2115</v>
+        <v>2114</v>
       </c>
       <c r="I1316" s="47">
         <v>281440</v>
@@ -28603,7 +28600,7 @@
         <v>561</v>
       </c>
       <c r="C1317" t="s">
-        <v>2116</v>
+        <v>2115</v>
       </c>
       <c r="I1317" s="47">
         <v>281443</v>
@@ -28617,7 +28614,7 @@
         <v>562</v>
       </c>
       <c r="C1318" t="s">
-        <v>2117</v>
+        <v>2116</v>
       </c>
       <c r="I1318" s="47">
         <v>281444</v>
@@ -28631,7 +28628,7 @@
         <v>563</v>
       </c>
       <c r="C1319" t="s">
-        <v>2118</v>
+        <v>2117</v>
       </c>
       <c r="I1319" s="47">
         <v>281445</v>
@@ -28645,7 +28642,7 @@
         <v>564</v>
       </c>
       <c r="C1320" t="s">
-        <v>2119</v>
+        <v>2118</v>
       </c>
       <c r="I1320" s="47">
         <v>281446</v>
@@ -28659,7 +28656,7 @@
         <v>565</v>
       </c>
       <c r="C1321" t="s">
-        <v>2120</v>
+        <v>2119</v>
       </c>
       <c r="I1321" s="47">
         <v>281447</v>
@@ -28673,7 +28670,7 @@
         <v>566</v>
       </c>
       <c r="C1322" t="s">
-        <v>2121</v>
+        <v>2120</v>
       </c>
       <c r="I1322" s="47">
         <v>281448</v>
@@ -28687,7 +28684,7 @@
         <v>567</v>
       </c>
       <c r="C1323" t="s">
-        <v>2122</v>
+        <v>2121</v>
       </c>
       <c r="I1323" s="47">
         <v>281449</v>
@@ -28701,7 +28698,7 @@
         <v>568</v>
       </c>
       <c r="C1324" t="s">
-        <v>2123</v>
+        <v>2122</v>
       </c>
       <c r="I1324" s="47">
         <v>281450</v>
@@ -28715,7 +28712,7 @@
         <v>569</v>
       </c>
       <c r="C1325" t="s">
-        <v>2124</v>
+        <v>2123</v>
       </c>
       <c r="I1325" s="47">
         <v>281451</v>
@@ -28729,7 +28726,7 @@
         <v>570</v>
       </c>
       <c r="C1326" t="s">
-        <v>2125</v>
+        <v>2124</v>
       </c>
       <c r="I1326" s="47">
         <v>281452</v>
@@ -28743,7 +28740,7 @@
         <v>571</v>
       </c>
       <c r="C1327" t="s">
-        <v>2126</v>
+        <v>2125</v>
       </c>
       <c r="I1327" s="47">
         <v>281452</v>
@@ -28757,7 +28754,7 @@
         <v>572</v>
       </c>
       <c r="C1328" t="s">
-        <v>2127</v>
+        <v>2126</v>
       </c>
       <c r="I1328" s="47">
         <v>281454</v>
@@ -28771,7 +28768,7 @@
         <v>573</v>
       </c>
       <c r="C1329" t="s">
-        <v>2128</v>
+        <v>2127</v>
       </c>
       <c r="I1329" s="47">
         <v>281455</v>
@@ -28785,7 +28782,7 @@
         <v>574</v>
       </c>
       <c r="C1330" t="s">
-        <v>2129</v>
+        <v>2128</v>
       </c>
       <c r="I1330" s="47">
         <v>281456</v>
@@ -28799,7 +28796,7 @@
         <v>575</v>
       </c>
       <c r="C1331" t="s">
-        <v>2130</v>
+        <v>2129</v>
       </c>
       <c r="I1331" s="47">
         <v>281456</v>
@@ -28813,7 +28810,7 @@
         <v>576</v>
       </c>
       <c r="C1332" t="s">
-        <v>2131</v>
+        <v>2130</v>
       </c>
       <c r="I1332" s="47">
         <v>281458</v>
@@ -28827,7 +28824,7 @@
         <v>577</v>
       </c>
       <c r="C1333" t="s">
-        <v>2132</v>
+        <v>2131</v>
       </c>
       <c r="I1333" s="47">
         <v>281458</v>
@@ -28841,7 +28838,7 @@
         <v>578</v>
       </c>
       <c r="C1334" t="s">
-        <v>2133</v>
+        <v>2132</v>
       </c>
       <c r="I1334" s="47">
         <v>281460</v>
@@ -28869,7 +28866,7 @@
         <v>580</v>
       </c>
       <c r="C1336" t="s">
-        <v>2134</v>
+        <v>2133</v>
       </c>
       <c r="I1336" s="47">
         <v>281462</v>
@@ -28883,7 +28880,7 @@
         <v>581</v>
       </c>
       <c r="C1337" t="s">
-        <v>2135</v>
+        <v>2134</v>
       </c>
       <c r="I1337" s="47">
         <v>281463</v>
@@ -28897,7 +28894,7 @@
         <v>582</v>
       </c>
       <c r="C1338" t="s">
-        <v>2136</v>
+        <v>2135</v>
       </c>
       <c r="I1338" s="47">
         <v>281464</v>
@@ -28911,7 +28908,7 @@
         <v>583</v>
       </c>
       <c r="C1339" t="s">
-        <v>2137</v>
+        <v>2136</v>
       </c>
       <c r="I1339" s="47">
         <v>281465</v>
@@ -28925,7 +28922,7 @@
         <v>584</v>
       </c>
       <c r="C1340" t="s">
-        <v>2138</v>
+        <v>2137</v>
       </c>
       <c r="I1340" s="47">
         <v>281466</v>
@@ -28939,7 +28936,7 @@
         <v>585</v>
       </c>
       <c r="C1341" t="s">
-        <v>2139</v>
+        <v>2138</v>
       </c>
       <c r="I1341" s="47">
         <v>281466</v>
@@ -28953,7 +28950,7 @@
         <v>586</v>
       </c>
       <c r="C1342" t="s">
-        <v>2140</v>
+        <v>2139</v>
       </c>
       <c r="I1342" s="47">
         <v>281468</v>
@@ -28967,7 +28964,7 @@
         <v>587</v>
       </c>
       <c r="C1343" t="s">
-        <v>2141</v>
+        <v>2140</v>
       </c>
       <c r="I1343" s="47">
         <v>281469</v>
@@ -28981,7 +28978,7 @@
         <v>588</v>
       </c>
       <c r="C1344" t="s">
-        <v>2142</v>
+        <v>2141</v>
       </c>
       <c r="I1344" s="47">
         <v>281469</v>
@@ -28995,7 +28992,7 @@
         <v>589</v>
       </c>
       <c r="C1345" t="s">
-        <v>2143</v>
+        <v>2142</v>
       </c>
       <c r="I1345" s="47">
         <v>281471</v>
@@ -29023,7 +29020,7 @@
         <v>591</v>
       </c>
       <c r="C1347" t="s">
-        <v>2144</v>
+        <v>2143</v>
       </c>
       <c r="I1347" s="47">
         <v>281473</v>
@@ -29037,7 +29034,7 @@
         <v>592</v>
       </c>
       <c r="C1348" t="s">
-        <v>2145</v>
+        <v>2144</v>
       </c>
       <c r="I1348" s="47">
         <v>281474</v>
@@ -29051,7 +29048,7 @@
         <v>593</v>
       </c>
       <c r="C1349" t="s">
-        <v>2146</v>
+        <v>2145</v>
       </c>
       <c r="I1349" s="47">
         <v>281475</v>
@@ -29065,7 +29062,7 @@
         <v>594</v>
       </c>
       <c r="C1350" t="s">
-        <v>2147</v>
+        <v>2146</v>
       </c>
       <c r="I1350" s="47">
         <v>281476</v>
@@ -29079,7 +29076,7 @@
         <v>595</v>
       </c>
       <c r="C1351" t="s">
-        <v>2148</v>
+        <v>2147</v>
       </c>
       <c r="I1351" s="47">
         <v>281477</v>
@@ -29093,7 +29090,7 @@
         <v>596</v>
       </c>
       <c r="C1352" t="s">
-        <v>2149</v>
+        <v>2148</v>
       </c>
       <c r="I1352" s="47">
         <v>281478</v>
@@ -29107,7 +29104,7 @@
         <v>597</v>
       </c>
       <c r="C1353" t="s">
-        <v>2150</v>
+        <v>2149</v>
       </c>
       <c r="I1353" s="47">
         <v>281479</v>
@@ -29121,7 +29118,7 @@
         <v>598</v>
       </c>
       <c r="C1354" t="s">
-        <v>2151</v>
+        <v>2150</v>
       </c>
       <c r="I1354" s="47">
         <v>281480</v>
@@ -29135,7 +29132,7 @@
         <v>599</v>
       </c>
       <c r="C1355" t="s">
-        <v>2152</v>
+        <v>2151</v>
       </c>
       <c r="I1355" s="47">
         <v>281481</v>
@@ -29149,7 +29146,7 @@
         <v>600</v>
       </c>
       <c r="C1356" t="s">
-        <v>2153</v>
+        <v>2152</v>
       </c>
       <c r="I1356" s="47">
         <v>281482</v>
@@ -29163,7 +29160,7 @@
         <v>601</v>
       </c>
       <c r="C1357" t="s">
-        <v>2148</v>
+        <v>2147</v>
       </c>
       <c r="I1357" s="47">
         <v>281483</v>
@@ -29177,7 +29174,7 @@
         <v>602</v>
       </c>
       <c r="C1358" t="s">
-        <v>2154</v>
+        <v>2153</v>
       </c>
       <c r="I1358" s="47">
         <v>281484</v>
@@ -29191,7 +29188,7 @@
         <v>603</v>
       </c>
       <c r="C1359" t="s">
-        <v>2155</v>
+        <v>2154</v>
       </c>
       <c r="I1359" s="47">
         <v>281485</v>
@@ -29205,7 +29202,7 @@
         <v>604</v>
       </c>
       <c r="C1360" t="s">
-        <v>2132</v>
+        <v>2131</v>
       </c>
       <c r="I1360" s="47">
         <v>281486</v>
@@ -29219,7 +29216,7 @@
         <v>605</v>
       </c>
       <c r="C1361" t="s">
-        <v>2156</v>
+        <v>2155</v>
       </c>
       <c r="I1361" s="47">
         <v>281487</v>
@@ -29233,7 +29230,7 @@
         <v>606</v>
       </c>
       <c r="C1362" t="s">
-        <v>2157</v>
+        <v>2156</v>
       </c>
       <c r="I1362" s="47">
         <v>281488</v>
@@ -29247,7 +29244,7 @@
         <v>607</v>
       </c>
       <c r="C1363" t="s">
-        <v>2158</v>
+        <v>2157</v>
       </c>
       <c r="I1363" s="47">
         <v>281489</v>
@@ -29261,7 +29258,7 @@
         <v>608</v>
       </c>
       <c r="C1364" t="s">
-        <v>2159</v>
+        <v>2158</v>
       </c>
       <c r="I1364" s="47">
         <v>281490</v>
@@ -29275,7 +29272,7 @@
         <v>609</v>
       </c>
       <c r="C1365" t="s">
-        <v>2160</v>
+        <v>2159</v>
       </c>
       <c r="I1365" s="47">
         <v>281491</v>
@@ -29289,7 +29286,7 @@
         <v>610</v>
       </c>
       <c r="C1366" t="s">
-        <v>2154</v>
+        <v>2153</v>
       </c>
       <c r="I1366" s="47">
         <v>281492</v>
@@ -29443,7 +29440,7 @@
         <v>621</v>
       </c>
       <c r="C1377" t="s">
-        <v>2192</v>
+        <v>2191</v>
       </c>
       <c r="I1377" s="47">
         <v>281552</v>
@@ -29485,7 +29482,7 @@
         <v>624</v>
       </c>
       <c r="C1380" t="s">
-        <v>2240</v>
+        <v>2239</v>
       </c>
       <c r="I1380" s="47">
         <v>281604</v>
@@ -29499,7 +29496,7 @@
         <v>625</v>
       </c>
       <c r="C1381" t="s">
-        <v>2241</v>
+        <v>2240</v>
       </c>
       <c r="I1381" s="47">
         <v>281604</v>
@@ -29513,7 +29510,7 @@
         <v>626</v>
       </c>
       <c r="C1382" t="s">
-        <v>2242</v>
+        <v>2241</v>
       </c>
       <c r="I1382" s="47">
         <v>281606</v>
@@ -29527,7 +29524,7 @@
         <v>627</v>
       </c>
       <c r="C1383" t="s">
-        <v>2243</v>
+        <v>2242</v>
       </c>
       <c r="I1383" s="47">
         <v>281607</v>
@@ -29541,7 +29538,7 @@
         <v>628</v>
       </c>
       <c r="C1384" t="s">
-        <v>2244</v>
+        <v>2243</v>
       </c>
       <c r="I1384" s="47">
         <v>281608</v>
@@ -29555,7 +29552,7 @@
         <v>629</v>
       </c>
       <c r="C1385" t="s">
-        <v>2245</v>
+        <v>2244</v>
       </c>
       <c r="I1385" s="47">
         <v>281609</v>
@@ -29569,7 +29566,7 @@
         <v>630</v>
       </c>
       <c r="C1386" t="s">
-        <v>2246</v>
+        <v>2245</v>
       </c>
       <c r="I1386" s="47">
         <v>281610</v>
@@ -29583,7 +29580,7 @@
         <v>631</v>
       </c>
       <c r="C1387" t="s">
-        <v>2247</v>
+        <v>2246</v>
       </c>
       <c r="I1387" s="47">
         <v>281611</v>
@@ -29597,7 +29594,7 @@
         <v>632</v>
       </c>
       <c r="C1388" t="s">
-        <v>2248</v>
+        <v>2247</v>
       </c>
       <c r="I1388" s="47">
         <v>281611</v>
@@ -29611,7 +29608,7 @@
         <v>633</v>
       </c>
       <c r="C1389" t="s">
-        <v>2249</v>
+        <v>2248</v>
       </c>
       <c r="I1389" s="47">
         <v>281613</v>
@@ -29625,7 +29622,7 @@
         <v>634</v>
       </c>
       <c r="C1390" t="s">
-        <v>2250</v>
+        <v>2249</v>
       </c>
       <c r="I1390" s="47">
         <v>281614</v>
@@ -29639,7 +29636,7 @@
         <v>635</v>
       </c>
       <c r="C1391" t="s">
-        <v>2251</v>
+        <v>2250</v>
       </c>
       <c r="I1391" s="47">
         <v>281614</v>
@@ -29653,7 +29650,7 @@
         <v>636</v>
       </c>
       <c r="C1392" t="s">
-        <v>2252</v>
+        <v>2251</v>
       </c>
       <c r="I1392" s="47">
         <v>281616</v>
@@ -29667,7 +29664,7 @@
         <v>637</v>
       </c>
       <c r="C1393" t="s">
-        <v>2253</v>
+        <v>2252</v>
       </c>
       <c r="I1393" s="47">
         <v>281617</v>
@@ -29681,7 +29678,7 @@
         <v>638</v>
       </c>
       <c r="C1394" t="s">
-        <v>2254</v>
+        <v>2253</v>
       </c>
       <c r="I1394" s="47">
         <v>281618</v>
@@ -29695,7 +29692,7 @@
         <v>639</v>
       </c>
       <c r="C1395" t="s">
-        <v>2255</v>
+        <v>2254</v>
       </c>
       <c r="I1395" s="47">
         <v>281619</v>
@@ -29709,7 +29706,7 @@
         <v>640</v>
       </c>
       <c r="C1396" t="s">
-        <v>2256</v>
+        <v>2255</v>
       </c>
       <c r="I1396" s="47">
         <v>281620</v>
@@ -29723,7 +29720,7 @@
         <v>641</v>
       </c>
       <c r="C1397" t="s">
-        <v>2257</v>
+        <v>2256</v>
       </c>
       <c r="I1397" s="47">
         <v>281620</v>
@@ -29737,7 +29734,7 @@
         <v>642</v>
       </c>
       <c r="C1398" t="s">
-        <v>2258</v>
+        <v>2257</v>
       </c>
       <c r="I1398" s="47">
         <v>281622</v>
@@ -29751,7 +29748,7 @@
         <v>643</v>
       </c>
       <c r="C1399" t="s">
-        <v>2259</v>
+        <v>2258</v>
       </c>
       <c r="I1399" s="47">
         <v>281622</v>
@@ -29765,7 +29762,7 @@
         <v>644</v>
       </c>
       <c r="C1400" t="s">
-        <v>2260</v>
+        <v>2259</v>
       </c>
       <c r="I1400" s="47">
         <v>281624</v>
@@ -29779,7 +29776,7 @@
         <v>645</v>
       </c>
       <c r="C1401" t="s">
-        <v>2261</v>
+        <v>2260</v>
       </c>
       <c r="I1401" s="47">
         <v>281624</v>
@@ -29793,7 +29790,7 @@
         <v>646</v>
       </c>
       <c r="C1402" t="s">
-        <v>2262</v>
+        <v>2261</v>
       </c>
       <c r="I1402" s="47">
         <v>281626</v>
@@ -29807,7 +29804,7 @@
         <v>647</v>
       </c>
       <c r="C1403" t="s">
-        <v>2263</v>
+        <v>2262</v>
       </c>
       <c r="I1403" s="47">
         <v>281626</v>
@@ -29821,7 +29818,7 @@
         <v>648</v>
       </c>
       <c r="C1404" t="s">
-        <v>2264</v>
+        <v>2263</v>
       </c>
       <c r="I1404" s="47">
         <v>281628</v>
@@ -29835,7 +29832,7 @@
         <v>649</v>
       </c>
       <c r="C1405" t="s">
-        <v>2265</v>
+        <v>2264</v>
       </c>
       <c r="I1405" s="47">
         <v>281629</v>
@@ -29849,7 +29846,7 @@
         <v>650</v>
       </c>
       <c r="C1406" t="s">
-        <v>2266</v>
+        <v>2265</v>
       </c>
       <c r="I1406" s="47">
         <v>281629</v>
@@ -29863,7 +29860,7 @@
         <v>651</v>
       </c>
       <c r="C1407" t="s">
-        <v>2267</v>
+        <v>2266</v>
       </c>
       <c r="I1407" s="47">
         <v>281631</v>
@@ -29877,7 +29874,7 @@
         <v>652</v>
       </c>
       <c r="C1408" t="s">
-        <v>2268</v>
+        <v>2267</v>
       </c>
       <c r="I1408" s="47">
         <v>281631</v>
@@ -29891,7 +29888,7 @@
         <v>653</v>
       </c>
       <c r="C1409" t="s">
-        <v>2269</v>
+        <v>2268</v>
       </c>
       <c r="I1409" s="47">
         <v>281631</v>
@@ -29905,7 +29902,7 @@
         <v>654</v>
       </c>
       <c r="C1410" t="s">
-        <v>2270</v>
+        <v>2269</v>
       </c>
       <c r="I1410" s="47">
         <v>281631</v>
@@ -29919,7 +29916,7 @@
         <v>655</v>
       </c>
       <c r="C1411" t="s">
-        <v>2271</v>
+        <v>2270</v>
       </c>
       <c r="I1411" s="47">
         <v>281631</v>
@@ -29933,7 +29930,7 @@
         <v>656</v>
       </c>
       <c r="C1412" t="s">
-        <v>2272</v>
+        <v>2271</v>
       </c>
       <c r="I1412" s="47">
         <v>281636</v>
@@ -29947,7 +29944,7 @@
         <v>657</v>
       </c>
       <c r="C1413" t="s">
-        <v>2273</v>
+        <v>2272</v>
       </c>
       <c r="I1413" s="47">
         <v>281637</v>
@@ -29961,7 +29958,7 @@
         <v>658</v>
       </c>
       <c r="C1414" t="s">
-        <v>2274</v>
+        <v>2273</v>
       </c>
       <c r="I1414" s="47">
         <v>281638</v>
@@ -29975,7 +29972,7 @@
         <v>659</v>
       </c>
       <c r="C1415" t="s">
-        <v>2275</v>
+        <v>2274</v>
       </c>
       <c r="I1415" s="47">
         <v>281639</v>
@@ -29989,7 +29986,7 @@
         <v>660</v>
       </c>
       <c r="C1416" t="s">
-        <v>2276</v>
+        <v>2275</v>
       </c>
       <c r="I1416" s="47">
         <v>281639</v>
@@ -30003,7 +30000,7 @@
         <v>661</v>
       </c>
       <c r="C1417" t="s">
-        <v>2277</v>
+        <v>2276</v>
       </c>
       <c r="I1417" s="47">
         <v>281641</v>
@@ -30031,7 +30028,7 @@
         <v>663</v>
       </c>
       <c r="C1419" t="s">
-        <v>2278</v>
+        <v>2277</v>
       </c>
       <c r="I1419" s="47">
         <v>281642</v>
@@ -30045,7 +30042,7 @@
         <v>664</v>
       </c>
       <c r="C1420" t="s">
-        <v>2279</v>
+        <v>2278</v>
       </c>
       <c r="I1420" s="47">
         <v>281644</v>
@@ -30059,7 +30056,7 @@
         <v>665</v>
       </c>
       <c r="C1421" t="s">
-        <v>2280</v>
+        <v>2279</v>
       </c>
       <c r="I1421" s="47">
         <v>281645</v>
@@ -30073,7 +30070,7 @@
         <v>666</v>
       </c>
       <c r="C1422" t="s">
-        <v>2281</v>
+        <v>2280</v>
       </c>
       <c r="I1422" s="47">
         <v>281646</v>
@@ -30087,7 +30084,7 @@
         <v>667</v>
       </c>
       <c r="C1423" t="s">
-        <v>2282</v>
+        <v>2281</v>
       </c>
       <c r="I1423" s="47">
         <v>281646</v>
@@ -30101,7 +30098,7 @@
         <v>668</v>
       </c>
       <c r="C1424" t="s">
-        <v>2283</v>
+        <v>2282</v>
       </c>
       <c r="I1424" s="47">
         <v>281646</v>
@@ -30115,7 +30112,7 @@
         <v>669</v>
       </c>
       <c r="C1425" t="s">
-        <v>2284</v>
+        <v>2283</v>
       </c>
       <c r="I1425" s="47">
         <v>281646</v>
@@ -30129,7 +30126,7 @@
         <v>670</v>
       </c>
       <c r="C1426" t="s">
-        <v>2285</v>
+        <v>2284</v>
       </c>
       <c r="I1426" s="47">
         <v>281650</v>
@@ -30143,7 +30140,7 @@
         <v>671</v>
       </c>
       <c r="C1427" t="s">
-        <v>2286</v>
+        <v>2285</v>
       </c>
       <c r="I1427" s="47">
         <v>281650</v>
@@ -30157,7 +30154,7 @@
         <v>672</v>
       </c>
       <c r="C1428" t="s">
-        <v>2261</v>
+        <v>2260</v>
       </c>
       <c r="I1428" s="47">
         <v>281650</v>
@@ -30171,7 +30168,7 @@
         <v>673</v>
       </c>
       <c r="C1429" t="s">
-        <v>2287</v>
+        <v>2286</v>
       </c>
       <c r="I1429" s="47">
         <v>281650</v>
@@ -30185,7 +30182,7 @@
         <v>674</v>
       </c>
       <c r="C1430" t="s">
-        <v>2288</v>
+        <v>2287</v>
       </c>
       <c r="I1430" s="47">
         <v>281654</v>
@@ -30199,7 +30196,7 @@
         <v>675</v>
       </c>
       <c r="C1431" t="s">
-        <v>2289</v>
+        <v>2288</v>
       </c>
       <c r="I1431" s="47">
         <v>281654</v>
@@ -30213,7 +30210,7 @@
         <v>676</v>
       </c>
       <c r="C1432" t="s">
-        <v>2290</v>
+        <v>2289</v>
       </c>
       <c r="I1432" s="47">
         <v>281656</v>
@@ -30227,7 +30224,7 @@
         <v>677</v>
       </c>
       <c r="C1433" t="s">
-        <v>2075</v>
+        <v>2074</v>
       </c>
       <c r="I1433" s="47">
         <v>281656</v>
@@ -30241,7 +30238,7 @@
         <v>678</v>
       </c>
       <c r="C1434" t="s">
-        <v>2291</v>
+        <v>2290</v>
       </c>
       <c r="I1434" s="47">
         <v>281656</v>
@@ -30255,7 +30252,7 @@
         <v>679</v>
       </c>
       <c r="C1435" t="s">
-        <v>2292</v>
+        <v>2291</v>
       </c>
       <c r="I1435" s="47">
         <v>281656</v>
@@ -30269,7 +30266,7 @@
         <v>680</v>
       </c>
       <c r="C1436" t="s">
-        <v>2293</v>
+        <v>2292</v>
       </c>
       <c r="I1436" s="47">
         <v>281656</v>
@@ -30283,7 +30280,7 @@
         <v>681</v>
       </c>
       <c r="C1437" t="s">
-        <v>2294</v>
+        <v>2293</v>
       </c>
       <c r="I1437" s="47">
         <v>281656</v>
@@ -30297,7 +30294,7 @@
         <v>682</v>
       </c>
       <c r="C1438" t="s">
-        <v>2295</v>
+        <v>2294</v>
       </c>
       <c r="I1438" s="47">
         <v>281662</v>
@@ -30311,7 +30308,7 @@
         <v>683</v>
       </c>
       <c r="C1439" t="s">
-        <v>2296</v>
+        <v>2295</v>
       </c>
       <c r="I1439" s="47">
         <v>281662</v>
@@ -30325,7 +30322,7 @@
         <v>684</v>
       </c>
       <c r="C1440" t="s">
-        <v>2297</v>
+        <v>2296</v>
       </c>
       <c r="I1440" s="47">
         <v>281662</v>
@@ -30339,7 +30336,7 @@
         <v>685</v>
       </c>
       <c r="C1441" t="s">
-        <v>2298</v>
+        <v>2297</v>
       </c>
       <c r="I1441" s="47">
         <v>281662</v>
@@ -30353,7 +30350,7 @@
         <v>686</v>
       </c>
       <c r="C1442" t="s">
-        <v>2299</v>
+        <v>2298</v>
       </c>
       <c r="I1442" s="47">
         <v>281666</v>
@@ -30367,7 +30364,7 @@
         <v>687</v>
       </c>
       <c r="C1443" t="s">
-        <v>2300</v>
+        <v>2299</v>
       </c>
       <c r="I1443" s="47">
         <v>281666</v>
@@ -30381,7 +30378,7 @@
         <v>688</v>
       </c>
       <c r="C1444" t="s">
-        <v>2301</v>
+        <v>2300</v>
       </c>
       <c r="I1444" s="47">
         <v>281666</v>
@@ -30395,7 +30392,7 @@
         <v>689</v>
       </c>
       <c r="C1445" t="s">
-        <v>2302</v>
+        <v>2301</v>
       </c>
       <c r="I1445" s="47">
         <v>281669</v>
@@ -30409,7 +30406,7 @@
         <v>690</v>
       </c>
       <c r="C1446" t="s">
-        <v>2303</v>
+        <v>2302</v>
       </c>
       <c r="I1446" s="47">
         <v>281670</v>
@@ -30423,7 +30420,7 @@
         <v>691</v>
       </c>
       <c r="C1447" t="s">
-        <v>2304</v>
+        <v>2303</v>
       </c>
       <c r="I1447" s="47">
         <v>281671</v>
@@ -30437,7 +30434,7 @@
         <v>692</v>
       </c>
       <c r="C1448" t="s">
-        <v>2305</v>
+        <v>2304</v>
       </c>
       <c r="I1448" s="47">
         <v>281672</v>
@@ -30451,7 +30448,7 @@
         <v>693</v>
       </c>
       <c r="C1449" t="s">
-        <v>2306</v>
+        <v>2305</v>
       </c>
       <c r="I1449" s="47">
         <v>281672</v>
@@ -30465,7 +30462,7 @@
         <v>694</v>
       </c>
       <c r="C1450" t="s">
-        <v>2307</v>
+        <v>2306</v>
       </c>
       <c r="I1450" s="47">
         <v>281674</v>
@@ -30479,7 +30476,7 @@
         <v>695</v>
       </c>
       <c r="C1451" t="s">
-        <v>2308</v>
+        <v>2307</v>
       </c>
       <c r="I1451" s="47">
         <v>281675</v>
@@ -30493,7 +30490,7 @@
         <v>696</v>
       </c>
       <c r="C1452" t="s">
-        <v>2309</v>
+        <v>2308</v>
       </c>
       <c r="I1452" s="47">
         <v>281675</v>
@@ -30507,7 +30504,7 @@
         <v>697</v>
       </c>
       <c r="C1453" t="s">
-        <v>2310</v>
+        <v>2309</v>
       </c>
       <c r="I1453" s="47">
         <v>281677</v>
@@ -30521,7 +30518,7 @@
         <v>698</v>
       </c>
       <c r="C1454" t="s">
-        <v>2311</v>
+        <v>2310</v>
       </c>
       <c r="I1454" s="47">
         <v>281677</v>
@@ -30535,7 +30532,7 @@
         <v>699</v>
       </c>
       <c r="C1455" t="s">
-        <v>2312</v>
+        <v>2311</v>
       </c>
       <c r="I1455" s="47">
         <v>281679</v>
@@ -30549,7 +30546,7 @@
         <v>700</v>
       </c>
       <c r="C1456" t="s">
-        <v>2313</v>
+        <v>2312</v>
       </c>
       <c r="I1456" s="47">
         <v>281679</v>
@@ -30563,7 +30560,7 @@
         <v>701</v>
       </c>
       <c r="C1457" t="s">
-        <v>2309</v>
+        <v>2308</v>
       </c>
       <c r="I1457" s="47">
         <v>281681</v>
@@ -30577,7 +30574,7 @@
         <v>702</v>
       </c>
       <c r="C1458" t="s">
-        <v>2314</v>
+        <v>2313</v>
       </c>
       <c r="I1458" s="47">
         <v>281681</v>
@@ -30591,7 +30588,7 @@
         <v>703</v>
       </c>
       <c r="C1459" t="s">
-        <v>2315</v>
+        <v>2314</v>
       </c>
       <c r="I1459" s="47">
         <v>281683</v>
@@ -30605,7 +30602,7 @@
         <v>704</v>
       </c>
       <c r="C1460" t="s">
-        <v>2316</v>
+        <v>2315</v>
       </c>
       <c r="I1460" s="47">
         <v>281684</v>
@@ -30619,7 +30616,7 @@
         <v>705</v>
       </c>
       <c r="C1461" t="s">
-        <v>2317</v>
+        <v>2316</v>
       </c>
       <c r="I1461" s="47">
         <v>281684</v>
@@ -30633,7 +30630,7 @@
         <v>706</v>
       </c>
       <c r="C1462" t="s">
-        <v>2318</v>
+        <v>2317</v>
       </c>
       <c r="I1462" s="47">
         <v>281686</v>
@@ -30647,7 +30644,7 @@
         <v>707</v>
       </c>
       <c r="C1463" t="s">
-        <v>2319</v>
+        <v>2318</v>
       </c>
       <c r="I1463" s="47">
         <v>281687</v>
@@ -30661,7 +30658,7 @@
         <v>708</v>
       </c>
       <c r="C1464" t="s">
-        <v>2320</v>
+        <v>2319</v>
       </c>
       <c r="I1464" s="47">
         <v>281688</v>
@@ -30675,7 +30672,7 @@
         <v>709</v>
       </c>
       <c r="C1465" t="s">
-        <v>2321</v>
+        <v>2320</v>
       </c>
       <c r="I1465" s="47">
         <v>281689</v>
@@ -30689,7 +30686,7 @@
         <v>710</v>
       </c>
       <c r="C1466" t="s">
-        <v>2322</v>
+        <v>2321</v>
       </c>
       <c r="I1466" s="47">
         <v>281689</v>
@@ -30703,7 +30700,7 @@
         <v>711</v>
       </c>
       <c r="C1467" t="s">
-        <v>2323</v>
+        <v>2322</v>
       </c>
       <c r="I1467" s="47">
         <v>281689</v>
@@ -30717,7 +30714,7 @@
         <v>712</v>
       </c>
       <c r="C1468" t="s">
-        <v>2324</v>
+        <v>2323</v>
       </c>
       <c r="I1468" s="47">
         <v>281692</v>
@@ -30731,7 +30728,7 @@
         <v>713</v>
       </c>
       <c r="C1469" t="s">
-        <v>2325</v>
+        <v>2324</v>
       </c>
       <c r="I1469" s="47">
         <v>281693</v>
@@ -30745,7 +30742,7 @@
         <v>714</v>
       </c>
       <c r="C1470" t="s">
-        <v>2326</v>
+        <v>2325</v>
       </c>
       <c r="I1470" s="47">
         <v>281694</v>
@@ -30759,7 +30756,7 @@
         <v>715</v>
       </c>
       <c r="C1471" t="s">
-        <v>2327</v>
+        <v>2326</v>
       </c>
       <c r="I1471" s="47">
         <v>281695</v>
@@ -30773,7 +30770,7 @@
         <v>716</v>
       </c>
       <c r="C1472" t="s">
-        <v>2328</v>
+        <v>2327</v>
       </c>
       <c r="I1472" s="47">
         <v>281696</v>
@@ -30787,7 +30784,7 @@
         <v>717</v>
       </c>
       <c r="C1473" t="s">
-        <v>2329</v>
+        <v>2328</v>
       </c>
       <c r="I1473" s="47">
         <v>281697</v>
@@ -30801,7 +30798,7 @@
         <v>718</v>
       </c>
       <c r="C1474" t="s">
-        <v>2330</v>
+        <v>2329</v>
       </c>
       <c r="I1474" s="47">
         <v>281697</v>
@@ -30815,7 +30812,7 @@
         <v>719</v>
       </c>
       <c r="C1475" t="s">
-        <v>2279</v>
+        <v>2278</v>
       </c>
       <c r="I1475" s="47">
         <v>281699</v>
@@ -30829,7 +30826,7 @@
         <v>720</v>
       </c>
       <c r="C1476" t="s">
-        <v>2320</v>
+        <v>2319</v>
       </c>
       <c r="I1476" s="47">
         <v>281700</v>
@@ -30843,7 +30840,7 @@
         <v>721</v>
       </c>
       <c r="C1477" t="s">
-        <v>2264</v>
+        <v>2263</v>
       </c>
       <c r="I1477" s="47">
         <v>281700</v>
@@ -30857,7 +30854,7 @@
         <v>722</v>
       </c>
       <c r="C1478" t="s">
-        <v>2279</v>
+        <v>2278</v>
       </c>
       <c r="I1478" s="47">
         <v>281702</v>
@@ -30969,7 +30966,7 @@
         <v>730</v>
       </c>
       <c r="C1486" t="s">
-        <v>2383</v>
+        <v>2382</v>
       </c>
       <c r="I1486" s="47">
         <v>281808</v>
@@ -30983,7 +30980,7 @@
         <v>731</v>
       </c>
       <c r="C1487" t="s">
-        <v>2384</v>
+        <v>2383</v>
       </c>
       <c r="I1487" s="47">
         <v>281809</v>
@@ -30997,7 +30994,7 @@
         <v>732</v>
       </c>
       <c r="C1488" t="s">
-        <v>2385</v>
+        <v>2384</v>
       </c>
       <c r="I1488" s="47">
         <v>281810</v>
@@ -31011,7 +31008,7 @@
         <v>733</v>
       </c>
       <c r="C1489" t="s">
-        <v>2386</v>
+        <v>2385</v>
       </c>
       <c r="I1489" s="47">
         <v>281810</v>
@@ -31025,7 +31022,7 @@
         <v>734</v>
       </c>
       <c r="C1490" t="s">
-        <v>2387</v>
+        <v>2386</v>
       </c>
       <c r="I1490" s="47">
         <v>281810</v>
@@ -31039,7 +31036,7 @@
         <v>735</v>
       </c>
       <c r="C1491" t="s">
-        <v>2388</v>
+        <v>2387</v>
       </c>
       <c r="I1491" s="47">
         <v>281810</v>
@@ -31053,7 +31050,7 @@
         <v>736</v>
       </c>
       <c r="C1492" t="s">
-        <v>2389</v>
+        <v>2388</v>
       </c>
       <c r="I1492" s="47">
         <v>281814</v>
@@ -31067,7 +31064,7 @@
         <v>737</v>
       </c>
       <c r="C1493" t="s">
-        <v>2390</v>
+        <v>2389</v>
       </c>
       <c r="I1493" s="47">
         <v>281815</v>
@@ -31081,7 +31078,7 @@
         <v>738</v>
       </c>
       <c r="C1494" t="s">
-        <v>2391</v>
+        <v>2390</v>
       </c>
       <c r="I1494" s="47">
         <v>281815</v>
@@ -31095,7 +31092,7 @@
         <v>739</v>
       </c>
       <c r="C1495" t="s">
-        <v>2392</v>
+        <v>2391</v>
       </c>
       <c r="I1495" s="47">
         <v>281815</v>
@@ -31109,7 +31106,7 @@
         <v>740</v>
       </c>
       <c r="C1496" t="s">
-        <v>2393</v>
+        <v>2392</v>
       </c>
       <c r="I1496" s="47">
         <v>281818</v>
@@ -31123,7 +31120,7 @@
         <v>741</v>
       </c>
       <c r="C1497" t="s">
-        <v>2394</v>
+        <v>2393</v>
       </c>
       <c r="I1497" s="47">
         <v>281819</v>
@@ -31137,7 +31134,7 @@
         <v>742</v>
       </c>
       <c r="C1498" t="s">
-        <v>2395</v>
+        <v>2394</v>
       </c>
       <c r="I1498" s="47">
         <v>281820</v>
@@ -31151,7 +31148,7 @@
         <v>743</v>
       </c>
       <c r="C1499" t="s">
-        <v>2396</v>
+        <v>2395</v>
       </c>
       <c r="I1499" s="47">
         <v>281821</v>
@@ -31165,7 +31162,7 @@
         <v>744</v>
       </c>
       <c r="C1500" t="s">
-        <v>2397</v>
+        <v>2396</v>
       </c>
       <c r="I1500" s="47">
         <v>281822</v>
@@ -31179,7 +31176,7 @@
         <v>745</v>
       </c>
       <c r="C1501" t="s">
-        <v>2398</v>
+        <v>2397</v>
       </c>
       <c r="I1501" s="47">
         <v>281823</v>
@@ -31193,7 +31190,7 @@
         <v>746</v>
       </c>
       <c r="C1502" t="s">
-        <v>2245</v>
+        <v>2244</v>
       </c>
       <c r="I1502" s="47">
         <v>281824</v>
@@ -31207,7 +31204,7 @@
         <v>747</v>
       </c>
       <c r="C1503" t="s">
-        <v>2399</v>
+        <v>2398</v>
       </c>
       <c r="I1503" s="47">
         <v>281825</v>
@@ -31221,7 +31218,7 @@
         <v>748</v>
       </c>
       <c r="C1504" t="s">
-        <v>2400</v>
+        <v>2399</v>
       </c>
       <c r="I1504" s="47">
         <v>281825</v>
@@ -31235,7 +31232,7 @@
         <v>749</v>
       </c>
       <c r="C1505" t="s">
-        <v>2401</v>
+        <v>2400</v>
       </c>
       <c r="I1505" s="47">
         <v>281827</v>
@@ -31249,7 +31246,7 @@
         <v>750</v>
       </c>
       <c r="C1506" t="s">
-        <v>2402</v>
+        <v>2401</v>
       </c>
       <c r="I1506" s="47">
         <v>281828</v>
@@ -31263,7 +31260,7 @@
         <v>751</v>
       </c>
       <c r="C1507" t="s">
-        <v>2403</v>
+        <v>2402</v>
       </c>
       <c r="I1507" s="47">
         <v>281829</v>
@@ -31277,7 +31274,7 @@
         <v>752</v>
       </c>
       <c r="C1508" t="s">
-        <v>2404</v>
+        <v>2403</v>
       </c>
       <c r="I1508" s="47">
         <v>281830</v>
@@ -31291,7 +31288,7 @@
         <v>753</v>
       </c>
       <c r="C1509" t="s">
-        <v>2405</v>
+        <v>2404</v>
       </c>
       <c r="I1509" s="47">
         <v>281831</v>
@@ -31305,7 +31302,7 @@
         <v>754</v>
       </c>
       <c r="C1510" t="s">
-        <v>2406</v>
+        <v>2405</v>
       </c>
       <c r="I1510" s="47">
         <v>281832</v>
@@ -31319,7 +31316,7 @@
         <v>755</v>
       </c>
       <c r="C1511" t="s">
-        <v>2407</v>
+        <v>2406</v>
       </c>
       <c r="I1511" s="47">
         <v>281833</v>
@@ -31333,7 +31330,7 @@
         <v>756</v>
       </c>
       <c r="C1512" t="s">
-        <v>2123</v>
+        <v>2122</v>
       </c>
       <c r="I1512" s="47">
         <v>281834</v>
@@ -31347,7 +31344,7 @@
         <v>757</v>
       </c>
       <c r="C1513" t="s">
-        <v>2408</v>
+        <v>2407</v>
       </c>
       <c r="I1513" s="47">
         <v>281835</v>
@@ -31361,7 +31358,7 @@
         <v>758</v>
       </c>
       <c r="C1514" t="s">
-        <v>2409</v>
+        <v>2408</v>
       </c>
       <c r="I1514" s="47">
         <v>281836</v>
@@ -31375,7 +31372,7 @@
         <v>759</v>
       </c>
       <c r="C1515" t="s">
-        <v>2410</v>
+        <v>2409</v>
       </c>
       <c r="I1515" s="47">
         <v>281836</v>
@@ -31389,7 +31386,7 @@
         <v>760</v>
       </c>
       <c r="C1516" t="s">
-        <v>2411</v>
+        <v>2410</v>
       </c>
       <c r="I1516" s="47">
         <v>281838</v>
@@ -31403,7 +31400,7 @@
         <v>761</v>
       </c>
       <c r="C1517" t="s">
-        <v>2412</v>
+        <v>2411</v>
       </c>
       <c r="I1517" s="47">
         <v>281838</v>
@@ -31417,7 +31414,7 @@
         <v>762</v>
       </c>
       <c r="C1518" t="s">
-        <v>2413</v>
+        <v>2412</v>
       </c>
       <c r="I1518" s="47">
         <v>281840</v>
@@ -31431,7 +31428,7 @@
         <v>763</v>
       </c>
       <c r="C1519" t="s">
-        <v>2414</v>
+        <v>2413</v>
       </c>
       <c r="I1519" s="47">
         <v>281841</v>
@@ -31445,7 +31442,7 @@
         <v>764</v>
       </c>
       <c r="C1520" t="s">
-        <v>2415</v>
+        <v>2414</v>
       </c>
       <c r="I1520" s="47">
         <v>281842</v>
@@ -31473,7 +31470,7 @@
         <v>766</v>
       </c>
       <c r="C1522" t="s">
-        <v>2416</v>
+        <v>2415</v>
       </c>
       <c r="I1522" s="47">
         <v>281844</v>
@@ -31487,7 +31484,7 @@
         <v>767</v>
       </c>
       <c r="C1523" t="s">
-        <v>2417</v>
+        <v>2416</v>
       </c>
       <c r="I1523" s="47">
         <v>281845</v>
@@ -31501,7 +31498,7 @@
         <v>768</v>
       </c>
       <c r="C1524" t="s">
-        <v>2418</v>
+        <v>2417</v>
       </c>
       <c r="I1524" s="47">
         <v>281846</v>
@@ -31515,7 +31512,7 @@
         <v>769</v>
       </c>
       <c r="C1525" t="s">
-        <v>2419</v>
+        <v>2418</v>
       </c>
       <c r="I1525" s="47">
         <v>281847</v>
@@ -31529,7 +31526,7 @@
         <v>770</v>
       </c>
       <c r="C1526" t="s">
-        <v>2420</v>
+        <v>2419</v>
       </c>
       <c r="I1526" s="47">
         <v>281848</v>
@@ -31543,7 +31540,7 @@
         <v>771</v>
       </c>
       <c r="C1527" t="s">
-        <v>2421</v>
+        <v>2420</v>
       </c>
       <c r="I1527" s="47">
         <v>281849</v>
@@ -31557,7 +31554,7 @@
         <v>772</v>
       </c>
       <c r="C1528" t="s">
-        <v>2422</v>
+        <v>2421</v>
       </c>
       <c r="I1528" s="47">
         <v>281850</v>
@@ -31571,7 +31568,7 @@
         <v>773</v>
       </c>
       <c r="C1529" t="s">
-        <v>2423</v>
+        <v>2422</v>
       </c>
       <c r="I1529" s="47">
         <v>281851</v>
@@ -31585,7 +31582,7 @@
         <v>774</v>
       </c>
       <c r="C1530" t="s">
-        <v>2424</v>
+        <v>2423</v>
       </c>
       <c r="I1530" s="47">
         <v>281852</v>
@@ -31599,7 +31596,7 @@
         <v>775</v>
       </c>
       <c r="C1531" t="s">
-        <v>2425</v>
+        <v>2424</v>
       </c>
       <c r="I1531" s="47">
         <v>281853</v>
@@ -31613,7 +31610,7 @@
         <v>776</v>
       </c>
       <c r="C1532" t="s">
-        <v>2426</v>
+        <v>2425</v>
       </c>
       <c r="I1532" s="47">
         <v>281854</v>
@@ -31627,7 +31624,7 @@
         <v>777</v>
       </c>
       <c r="C1533" t="s">
-        <v>2427</v>
+        <v>2426</v>
       </c>
       <c r="I1533" s="47">
         <v>281855</v>
@@ -31641,7 +31638,7 @@
         <v>778</v>
       </c>
       <c r="C1534" t="s">
-        <v>2428</v>
+        <v>2427</v>
       </c>
       <c r="I1534" s="47">
         <v>281855</v>
@@ -31655,7 +31652,7 @@
         <v>779</v>
       </c>
       <c r="C1535" t="s">
-        <v>2429</v>
+        <v>2428</v>
       </c>
       <c r="I1535" s="47">
         <v>281857</v>
@@ -31669,7 +31666,7 @@
         <v>780</v>
       </c>
       <c r="C1536" t="s">
-        <v>2430</v>
+        <v>2429</v>
       </c>
       <c r="I1536" s="47">
         <v>281857</v>
@@ -31683,7 +31680,7 @@
         <v>781</v>
       </c>
       <c r="C1537" t="s">
-        <v>2431</v>
+        <v>2430</v>
       </c>
       <c r="I1537" s="47">
         <v>281859</v>
@@ -31697,7 +31694,7 @@
         <v>782</v>
       </c>
       <c r="C1538" t="s">
-        <v>2432</v>
+        <v>2431</v>
       </c>
       <c r="I1538" s="47">
         <v>281859</v>
@@ -31711,7 +31708,7 @@
         <v>783</v>
       </c>
       <c r="C1539" t="s">
-        <v>2251</v>
+        <v>2250</v>
       </c>
       <c r="I1539" s="47">
         <v>281861</v>
@@ -31725,7 +31722,7 @@
         <v>784</v>
       </c>
       <c r="C1540" t="s">
-        <v>2433</v>
+        <v>2432</v>
       </c>
       <c r="I1540" s="47">
         <v>281862</v>
@@ -31739,7 +31736,7 @@
         <v>785</v>
       </c>
       <c r="C1541" t="s">
-        <v>2434</v>
+        <v>2433</v>
       </c>
       <c r="I1541" s="47">
         <v>281863</v>
@@ -31753,7 +31750,7 @@
         <v>786</v>
       </c>
       <c r="C1542" t="s">
-        <v>2435</v>
+        <v>2434</v>
       </c>
       <c r="I1542" s="47">
         <v>281863</v>
@@ -31767,7 +31764,7 @@
         <v>787</v>
       </c>
       <c r="C1543" t="s">
-        <v>2436</v>
+        <v>2435</v>
       </c>
       <c r="I1543" s="47">
         <v>281863</v>
@@ -31781,7 +31778,7 @@
         <v>788</v>
       </c>
       <c r="C1544" t="s">
-        <v>2437</v>
+        <v>2436</v>
       </c>
       <c r="I1544" s="47">
         <v>281866</v>
@@ -31795,7 +31792,7 @@
         <v>789</v>
       </c>
       <c r="C1545" t="s">
-        <v>2438</v>
+        <v>2437</v>
       </c>
       <c r="I1545" s="47">
         <v>281867</v>
@@ -31809,7 +31806,7 @@
         <v>790</v>
       </c>
       <c r="C1546" t="s">
-        <v>2439</v>
+        <v>2438</v>
       </c>
       <c r="I1546" s="47">
         <v>281868</v>
@@ -31823,7 +31820,7 @@
         <v>791</v>
       </c>
       <c r="C1547" t="s">
-        <v>2389</v>
+        <v>2388</v>
       </c>
       <c r="I1547" s="47">
         <v>281869</v>
@@ -31837,7 +31834,7 @@
         <v>792</v>
       </c>
       <c r="C1548" t="s">
-        <v>2440</v>
+        <v>2439</v>
       </c>
       <c r="I1548" s="47">
         <v>281870</v>
@@ -31851,7 +31848,7 @@
         <v>793</v>
       </c>
       <c r="C1549" t="s">
-        <v>2441</v>
+        <v>2440</v>
       </c>
       <c r="I1549" s="47">
         <v>281871</v>
@@ -31865,7 +31862,7 @@
         <v>794</v>
       </c>
       <c r="C1550" t="s">
-        <v>2442</v>
+        <v>2441</v>
       </c>
       <c r="I1550" s="47">
         <v>281872</v>
@@ -31879,7 +31876,7 @@
         <v>795</v>
       </c>
       <c r="C1551" t="s">
-        <v>2443</v>
+        <v>2442</v>
       </c>
       <c r="I1551" s="47">
         <v>281873</v>
@@ -31893,7 +31890,7 @@
         <v>796</v>
       </c>
       <c r="C1552" t="s">
-        <v>2444</v>
+        <v>2443</v>
       </c>
       <c r="I1552" s="47">
         <v>281874</v>
@@ -31907,7 +31904,7 @@
         <v>797</v>
       </c>
       <c r="C1553" t="s">
-        <v>2445</v>
+        <v>2444</v>
       </c>
       <c r="I1553" s="47">
         <v>281875</v>
@@ -31921,7 +31918,7 @@
         <v>798</v>
       </c>
       <c r="C1554" t="s">
-        <v>2446</v>
+        <v>2445</v>
       </c>
       <c r="I1554" s="47">
         <v>281876</v>
@@ -31935,7 +31932,7 @@
         <v>799</v>
       </c>
       <c r="C1555" t="s">
-        <v>2447</v>
+        <v>2446</v>
       </c>
       <c r="I1555" s="47">
         <v>281877</v>
@@ -31949,7 +31946,7 @@
         <v>800</v>
       </c>
       <c r="C1556" t="s">
-        <v>2448</v>
+        <v>2447</v>
       </c>
       <c r="I1556" s="47">
         <v>281878</v>
@@ -31963,7 +31960,7 @@
         <v>801</v>
       </c>
       <c r="C1557" t="s">
-        <v>2449</v>
+        <v>2448</v>
       </c>
       <c r="I1557" s="47">
         <v>281879</v>
@@ -31977,7 +31974,7 @@
         <v>802</v>
       </c>
       <c r="C1558" t="s">
-        <v>2411</v>
+        <v>2410</v>
       </c>
       <c r="I1558" s="47">
         <v>281880</v>
@@ -32235,7 +32232,7 @@
         <v>258</v>
       </c>
       <c r="O6" s="2" t="s">
-        <v>2486</v>
+        <v>2485</v>
       </c>
     </row>
     <row r="7" spans="1:18" ht="14" x14ac:dyDescent="0.3">
@@ -32342,10 +32339,10 @@
         <v>276</v>
       </c>
       <c r="O10" s="2" t="s">
-        <v>2485</v>
+        <v>2484</v>
       </c>
       <c r="Q10" t="s">
-        <v>2490</v>
+        <v>2489</v>
       </c>
       <c r="R10" s="2" t="s">
         <v>272</v>
@@ -32374,10 +32371,10 @@
         <v>258</v>
       </c>
       <c r="O11" s="2" t="s">
-        <v>2487</v>
+        <v>2486</v>
       </c>
       <c r="P11" s="2" t="s">
-        <v>2563</v>
+        <v>2562</v>
       </c>
     </row>
     <row r="12" spans="1:18" ht="14" x14ac:dyDescent="0.3">
@@ -32403,7 +32400,7 @@
         <v>258</v>
       </c>
       <c r="O12" s="2" t="s">
-        <v>2488</v>
+        <v>2487</v>
       </c>
       <c r="P12" s="2" t="s">
         <v>283</v>
@@ -32562,10 +32559,10 @@
         <v>258</v>
       </c>
       <c r="Q18" s="43" t="s">
+        <v>2563</v>
+      </c>
+      <c r="R18" s="43" t="s">
         <v>2564</v>
-      </c>
-      <c r="R18" s="43" t="s">
-        <v>2565</v>
       </c>
     </row>
     <row r="19" spans="1:18" ht="14" x14ac:dyDescent="0.3">
@@ -32646,7 +32643,7 @@
         <v>258</v>
       </c>
       <c r="O21" s="2" t="s">
-        <v>2489</v>
+        <v>2488</v>
       </c>
     </row>
     <row r="22" spans="1:18" ht="14" x14ac:dyDescent="0.3">
@@ -34369,7 +34366,7 @@
         <v>251</v>
       </c>
       <c r="B119" s="8" t="s">
-        <v>2492</v>
+        <v>2491</v>
       </c>
       <c r="C119" s="8"/>
       <c r="D119" s="8"/>
@@ -34401,7 +34398,7 @@
         <v>320</v>
       </c>
       <c r="B120" s="2" t="s">
-        <v>2493</v>
+        <v>2492</v>
       </c>
       <c r="H120" s="2"/>
       <c r="I120" s="9" t="s">
@@ -34416,7 +34413,7 @@
         <v>251</v>
       </c>
       <c r="B121" s="2" t="s">
-        <v>2494</v>
+        <v>2493</v>
       </c>
       <c r="H121" s="2"/>
       <c r="M121" s="2" t="s">
@@ -34428,7 +34425,7 @@
         <v>247</v>
       </c>
       <c r="B122" s="2" t="s">
-        <v>2495</v>
+        <v>2494</v>
       </c>
       <c r="H122" s="2" t="s">
         <v>1077</v>
@@ -34445,7 +34442,7 @@
         <v>247</v>
       </c>
       <c r="B123" s="22" t="s">
-        <v>2496</v>
+        <v>2495</v>
       </c>
       <c r="H123" s="2" t="s">
         <v>1099</v>
@@ -34465,7 +34462,7 @@
         <v>247</v>
       </c>
       <c r="B124" s="30" t="s">
-        <v>2497</v>
+        <v>2496</v>
       </c>
       <c r="H124" s="2" t="s">
         <v>1080</v>
@@ -34485,7 +34482,7 @@
         <v>247</v>
       </c>
       <c r="B125" s="2" t="s">
-        <v>2498</v>
+        <v>2497</v>
       </c>
       <c r="H125" s="2" t="s">
         <v>324</v>
@@ -34509,7 +34506,7 @@
         <v>251</v>
       </c>
       <c r="B127" s="2" t="s">
-        <v>2499</v>
+        <v>2498</v>
       </c>
       <c r="H127" s="2"/>
       <c r="M127" s="2" t="s">
@@ -34521,7 +34518,7 @@
         <v>247</v>
       </c>
       <c r="B128" s="2" t="s">
-        <v>2500</v>
+        <v>2499</v>
       </c>
       <c r="H128" s="2" t="s">
         <v>322</v>
@@ -34538,7 +34535,7 @@
         <v>274</v>
       </c>
       <c r="B129" s="22" t="s">
-        <v>2501</v>
+        <v>2500</v>
       </c>
       <c r="H129" s="2" t="s">
         <v>1101</v>
@@ -34573,7 +34570,7 @@
         <v>274</v>
       </c>
       <c r="B130" s="30" t="s">
-        <v>2502</v>
+        <v>2501</v>
       </c>
       <c r="H130" s="2" t="s">
         <v>1102</v>
@@ -34608,10 +34605,10 @@
         <v>247</v>
       </c>
       <c r="B131" s="2" t="s">
+        <v>2502</v>
+      </c>
+      <c r="H131" s="2" t="s">
         <v>2503</v>
-      </c>
-      <c r="H131" s="2" t="s">
-        <v>2504</v>
       </c>
       <c r="I131" s="2" t="s">
         <v>325</v>
@@ -34631,7 +34628,7 @@
         <v>251</v>
       </c>
       <c r="B133" s="2" t="s">
-        <v>2505</v>
+        <v>2504</v>
       </c>
       <c r="H133" s="2"/>
       <c r="M133" s="2" t="s">
@@ -34643,7 +34640,7 @@
         <v>247</v>
       </c>
       <c r="B134" s="2" t="s">
-        <v>2506</v>
+        <v>2505</v>
       </c>
       <c r="H134" s="2" t="s">
         <v>323</v>
@@ -34660,7 +34657,7 @@
         <v>274</v>
       </c>
       <c r="B135" s="22" t="s">
-        <v>2507</v>
+        <v>2506</v>
       </c>
       <c r="H135" s="2" t="s">
         <v>1101</v>
@@ -34695,7 +34692,7 @@
         <v>274</v>
       </c>
       <c r="B136" s="30" t="s">
-        <v>2508</v>
+        <v>2507</v>
       </c>
       <c r="H136" s="2" t="s">
         <v>1102</v>
@@ -34730,10 +34727,10 @@
         <v>247</v>
       </c>
       <c r="B137" s="2" t="s">
+        <v>2508</v>
+      </c>
+      <c r="H137" s="2" t="s">
         <v>2509</v>
-      </c>
-      <c r="H137" s="2" t="s">
-        <v>2510</v>
       </c>
       <c r="I137" s="2" t="s">
         <v>325</v>
@@ -34753,7 +34750,7 @@
         <v>251</v>
       </c>
       <c r="B139" s="2" t="s">
-        <v>2511</v>
+        <v>2510</v>
       </c>
       <c r="H139" s="2"/>
       <c r="M139" s="2" t="s">
@@ -34765,7 +34762,7 @@
         <v>247</v>
       </c>
       <c r="B140" s="2" t="s">
-        <v>2512</v>
+        <v>2511</v>
       </c>
       <c r="H140" s="2" t="s">
         <v>324</v>
@@ -34782,10 +34779,10 @@
         <v>247</v>
       </c>
       <c r="B141" s="22" t="s">
+        <v>2512</v>
+      </c>
+      <c r="H141" s="2" t="s">
         <v>2513</v>
-      </c>
-      <c r="H141" s="2" t="s">
-        <v>2514</v>
       </c>
       <c r="I141" s="2" t="s">
         <v>1007</v>
@@ -34802,10 +34799,10 @@
         <v>247</v>
       </c>
       <c r="B142" s="30" t="s">
+        <v>2514</v>
+      </c>
+      <c r="H142" s="2" t="s">
         <v>2515</v>
-      </c>
-      <c r="H142" s="2" t="s">
-        <v>2516</v>
       </c>
       <c r="I142" s="2" t="s">
         <v>1023</v>
@@ -34822,10 +34819,10 @@
         <v>247</v>
       </c>
       <c r="B143" s="2" t="s">
+        <v>2516</v>
+      </c>
+      <c r="H143" s="2" t="s">
         <v>2517</v>
-      </c>
-      <c r="H143" s="2" t="s">
-        <v>2518</v>
       </c>
       <c r="I143" s="2" t="s">
         <v>325</v>
@@ -34845,7 +34842,7 @@
         <v>515</v>
       </c>
       <c r="B145" s="33" t="s">
-        <v>2519</v>
+        <v>2518</v>
       </c>
       <c r="H145" s="33" t="s">
         <v>590</v>
@@ -34854,7 +34851,7 @@
         <v>1068</v>
       </c>
       <c r="O145" s="34" t="s">
-        <v>2520</v>
+        <v>2519</v>
       </c>
     </row>
     <row r="146" spans="1:18" s="33" customFormat="1" ht="28" x14ac:dyDescent="0.3">
@@ -34862,7 +34859,7 @@
         <v>515</v>
       </c>
       <c r="B146" s="33" t="s">
-        <v>2521</v>
+        <v>2520</v>
       </c>
       <c r="H146" s="33" t="s">
         <v>590</v>
@@ -34871,7 +34868,7 @@
         <v>1069</v>
       </c>
       <c r="O146" s="34" t="s">
-        <v>2522</v>
+        <v>2521</v>
       </c>
     </row>
     <row r="147" spans="1:18" s="33" customFormat="1" ht="28" x14ac:dyDescent="0.3">
@@ -34879,7 +34876,7 @@
         <v>515</v>
       </c>
       <c r="B147" s="33" t="s">
-        <v>2523</v>
+        <v>2522</v>
       </c>
       <c r="H147" s="33" t="s">
         <v>590</v>
@@ -34888,7 +34885,7 @@
         <v>588</v>
       </c>
       <c r="O147" s="34" t="s">
-        <v>2524</v>
+        <v>2523</v>
       </c>
     </row>
     <row r="148" spans="1:18" s="33" customFormat="1" ht="14" x14ac:dyDescent="0.3">
@@ -34896,7 +34893,7 @@
         <v>515</v>
       </c>
       <c r="B148" s="33" t="s">
-        <v>2525</v>
+        <v>2524</v>
       </c>
       <c r="H148" s="33" t="s">
         <v>590</v>
@@ -34905,7 +34902,7 @@
         <v>1058</v>
       </c>
       <c r="O148" s="2" t="s">
-        <v>2526</v>
+        <v>2525</v>
       </c>
     </row>
     <row r="149" spans="1:18" s="33" customFormat="1" ht="14" x14ac:dyDescent="0.3">
@@ -34913,7 +34910,7 @@
         <v>515</v>
       </c>
       <c r="B149" s="33" t="s">
-        <v>2527</v>
+        <v>2526</v>
       </c>
       <c r="H149" s="33" t="s">
         <v>590</v>
@@ -34922,7 +34919,7 @@
         <v>1060</v>
       </c>
       <c r="O149" s="2" t="s">
-        <v>2528</v>
+        <v>2527</v>
       </c>
     </row>
     <row r="150" spans="1:18" ht="14" x14ac:dyDescent="0.3">
@@ -37767,10 +37764,10 @@
         <v>1206</v>
       </c>
       <c r="H318" s="2" t="s">
+        <v>2529</v>
+      </c>
+      <c r="I318" s="15" t="s">
         <v>2530</v>
-      </c>
-      <c r="I318" s="15" t="s">
-        <v>2531</v>
       </c>
       <c r="M318" s="2" t="s">
         <v>258</v>
@@ -37783,7 +37780,7 @@
         <v>247</v>
       </c>
       <c r="B319" s="2" t="s">
-        <v>2529</v>
+        <v>2528</v>
       </c>
       <c r="H319" s="2" t="s">
         <v>1162</v>
@@ -38084,7 +38081,7 @@
         <v>589</v>
       </c>
       <c r="I331" s="15" t="s">
-        <v>2531</v>
+        <v>2530</v>
       </c>
       <c r="J331" s="17"/>
       <c r="M331" s="2" t="s">
@@ -38098,10 +38095,10 @@
         <v>247</v>
       </c>
       <c r="B332" s="15" t="s">
-        <v>2532</v>
+        <v>2531</v>
       </c>
       <c r="H332" s="15" t="s">
-        <v>2537</v>
+        <v>2536</v>
       </c>
       <c r="I332" s="15" t="s">
         <v>325</v>
@@ -38373,7 +38370,7 @@
         <v>589</v>
       </c>
       <c r="I344" s="15" t="s">
-        <v>2531</v>
+        <v>2530</v>
       </c>
       <c r="J344" s="17"/>
       <c r="M344" s="2" t="s">
@@ -38393,10 +38390,10 @@
         <v>247</v>
       </c>
       <c r="B345" s="15" t="s">
-        <v>2533</v>
+        <v>2532</v>
       </c>
       <c r="H345" s="15" t="s">
-        <v>2535</v>
+        <v>2534</v>
       </c>
       <c r="I345" s="15" t="s">
         <v>325</v>
@@ -38628,7 +38625,7 @@
         <v>1233</v>
       </c>
       <c r="I357" s="15" t="s">
-        <v>2531</v>
+        <v>2530</v>
       </c>
       <c r="J357" s="17"/>
       <c r="M357" s="2" t="s">
@@ -38643,10 +38640,10 @@
         <v>247</v>
       </c>
       <c r="B358" s="15" t="s">
-        <v>2534</v>
+        <v>2533</v>
       </c>
       <c r="H358" s="15" t="s">
-        <v>2536</v>
+        <v>2535</v>
       </c>
       <c r="I358" s="15" t="s">
         <v>325</v>
@@ -38678,13 +38675,13 @@
         <v>515</v>
       </c>
       <c r="B361" s="33" t="s">
-        <v>2541</v>
+        <v>2540</v>
       </c>
       <c r="I361" s="33" t="s">
         <v>586</v>
       </c>
       <c r="O361" s="34" t="s">
-        <v>2539</v>
+        <v>2538</v>
       </c>
     </row>
     <row r="362" spans="1:17" s="33" customFormat="1" ht="13.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -38692,13 +38689,13 @@
         <v>515</v>
       </c>
       <c r="B362" s="33" t="s">
-        <v>2542</v>
+        <v>2541</v>
       </c>
       <c r="I362" s="33" t="s">
         <v>587</v>
       </c>
       <c r="O362" s="34" t="s">
-        <v>2540</v>
+        <v>2539</v>
       </c>
     </row>
     <row r="363" spans="1:17" s="33" customFormat="1" ht="13.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -38706,13 +38703,13 @@
         <v>515</v>
       </c>
       <c r="B363" s="33" t="s">
-        <v>2543</v>
+        <v>2542</v>
       </c>
       <c r="I363" s="33" t="s">
         <v>588</v>
       </c>
       <c r="O363" s="34" t="s">
-        <v>2544</v>
+        <v>2543</v>
       </c>
     </row>
     <row r="364" spans="1:17" ht="13.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -38876,12 +38873,12 @@
       </c>
       <c r="H374" s="15"/>
       <c r="I374" s="33" t="s">
-        <v>2531</v>
+        <v>2530</v>
       </c>
       <c r="J374" s="17"/>
       <c r="N374" s="15"/>
       <c r="O374" s="34" t="s">
-        <v>2538</v>
+        <v>2537</v>
       </c>
       <c r="Q374"/>
     </row>
@@ -38918,7 +38915,7 @@
         <v>665</v>
       </c>
       <c r="N378" s="33" t="s">
-        <v>2545</v>
+        <v>2544</v>
       </c>
       <c r="O378" s="34"/>
     </row>
@@ -38939,7 +38936,7 @@
         <v>665</v>
       </c>
       <c r="N379" s="33" t="s">
-        <v>2546</v>
+        <v>2545</v>
       </c>
       <c r="O379" s="34"/>
     </row>
@@ -40405,10 +40402,10 @@
         <v>903</v>
       </c>
       <c r="H469" s="2" t="s">
+        <v>2546</v>
+      </c>
+      <c r="I469" s="20" t="s">
         <v>2547</v>
-      </c>
-      <c r="I469" s="20" t="s">
-        <v>2548</v>
       </c>
       <c r="M469" s="2" t="s">
         <v>258</v>
@@ -45220,14 +45217,14 @@
         <v>998</v>
       </c>
       <c r="H711" s="3" t="s">
-        <v>2553</v>
+        <v>2552</v>
       </c>
       <c r="I711" s="41"/>
       <c r="M711" s="2" t="s">
         <v>262</v>
       </c>
       <c r="N711" s="15" t="s">
-        <v>2552</v>
+        <v>2551</v>
       </c>
       <c r="O711" s="15"/>
     </row>
@@ -45242,7 +45239,7 @@
         <v>589</v>
       </c>
       <c r="I712" s="15" t="s">
-        <v>2554</v>
+        <v>2553</v>
       </c>
       <c r="J712" s="2" t="s">
         <v>256</v>
@@ -45254,7 +45251,7 @@
         <v>262</v>
       </c>
       <c r="N712" s="15" t="s">
-        <v>2552</v>
+        <v>2551</v>
       </c>
       <c r="O712" s="15"/>
     </row>
@@ -45266,14 +45263,14 @@
         <v>1000</v>
       </c>
       <c r="H713" s="3" t="s">
-        <v>2555</v>
+        <v>2554</v>
       </c>
       <c r="I713" s="41"/>
       <c r="M713" s="2" t="s">
         <v>262</v>
       </c>
       <c r="N713" s="15" t="s">
-        <v>2551</v>
+        <v>2550</v>
       </c>
       <c r="O713" s="15"/>
     </row>
@@ -45288,7 +45285,7 @@
         <v>589</v>
       </c>
       <c r="I714" s="15" t="s">
-        <v>2556</v>
+        <v>2555</v>
       </c>
       <c r="J714" s="2" t="s">
         <v>256</v>
@@ -45300,7 +45297,7 @@
         <v>262</v>
       </c>
       <c r="N714" s="15" t="s">
-        <v>2551</v>
+        <v>2550</v>
       </c>
       <c r="O714" s="15"/>
     </row>
@@ -45309,7 +45306,7 @@
         <v>247</v>
       </c>
       <c r="B715" s="2" t="s">
-        <v>2549</v>
+        <v>2548</v>
       </c>
       <c r="H715" s="3" t="s">
         <v>1135</v>
@@ -45326,7 +45323,7 @@
         <v>274</v>
       </c>
       <c r="B716" s="2" t="s">
-        <v>2550</v>
+        <v>2549</v>
       </c>
       <c r="H716" s="15" t="s">
         <v>589</v>
